--- a/wwwroot/92/BoxBreakingReport.xlsx
+++ b/wwwroot/92/BoxBreakingReport.xlsx
@@ -14,6 +14,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="217">
   <si>
+    <t>SerialNo</t>
+  </si>
+  <si>
     <t>CatchNo</t>
   </si>
   <si>
@@ -65,10 +68,7 @@
     <t>BoxNo</t>
   </si>
   <si>
-    <t>OmrSerial</t>
-  </si>
-  <si>
-    <t>InnerBundlingSerial</t>
+    <t>Beejak</t>
   </si>
   <si>
     <t>BED103</t>
@@ -92,16 +92,16 @@
     <t>2001</t>
   </si>
   <si>
+    <t>BED104</t>
+  </si>
+  <si>
+    <t>11-02-2026</t>
+  </si>
+  <si>
+    <t>20 to 28</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>BED104</t>
-  </si>
-  <si>
-    <t>11-02-2026</t>
-  </si>
-  <si>
-    <t>20 to 28</t>
   </si>
   <si>
     <t>KP/II/1003/25</t>
@@ -670,8 +670,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
     </font>
@@ -696,8 +701,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -708,90 +714,93 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
-  <dimension ref="B1:T296"/>
+  <dimension ref="A1:S296"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
     <col min="2" max="2" width="16.057085037231445" customWidth="1"/>
     <col min="3" max="3" width="16.09404182434082" customWidth="1"/>
-    <col min="4" max="4" width="11.54150390625" customWidth="1"/>
+    <col min="4" max="4" width="11.811811447143555" customWidth="1"/>
     <col min="5" max="5" width="22.885726928710938" customWidth="1"/>
     <col min="6" max="6" width="13.382554054260254" customWidth="1"/>
-    <col min="7" max="7" width="9.146153450012207" customWidth="1"/>
-    <col min="8" max="8" width="11.75413990020752" customWidth="1"/>
-    <col min="9" max="9" width="10.625441551208496" customWidth="1"/>
+    <col min="7" max="7" width="9.218536376953125" customWidth="1"/>
+    <col min="8" max="8" width="11.907477378845215" customWidth="1"/>
+    <col min="9" max="9" width="10.976926803588867" customWidth="1"/>
     <col min="10" max="10" width="9.140625" customWidth="1"/>
-    <col min="11" max="11" width="10.764904975891113" customWidth="1"/>
-    <col min="12" max="12" width="9.573080062866211" customWidth="1"/>
+    <col min="11" max="11" width="11.134539604187012" customWidth="1"/>
+    <col min="12" max="12" width="9.52771282196045" customWidth="1"/>
     <col min="13" max="13" width="9.140625" customWidth="1"/>
     <col min="14" max="14" width="9.140625" customWidth="1"/>
     <col min="15" max="15" width="9.432053565979004" customWidth="1"/>
     <col min="16" max="16" width="9.140625" customWidth="1"/>
-    <col min="17" max="17" width="11.96428394317627" customWidth="1"/>
+    <col min="17" max="17" width="11.965397834777832" customWidth="1"/>
     <col min="18" max="18" width="9.140625" customWidth="1"/>
-    <col min="19" max="19" width="11.050959587097168" customWidth="1"/>
-    <col min="20" max="20" width="19.786996841430664" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="0" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="0" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="0" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="0" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="0" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2">
+      <c r="A2" s="0">
+        <v>1</v>
+      </c>
       <c r="B2" s="0" t="s">
         <v>19</v>
       </c>
@@ -842,15 +851,15 @@
         <v>25</v>
       </c>
       <c r="S2" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>26</v>
-      </c>
-      <c r="T2" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="0" t="s">
-        <v>27</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>20</v>
@@ -862,7 +871,7 @@
         <v>21</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3" s="0">
         <v>720</v>
@@ -887,7 +896,7 @@
         <v>28</v>
       </c>
       <c r="O3" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P3" s="0">
         <v>4</v>
@@ -899,13 +908,13 @@
         <v>25</v>
       </c>
       <c r="S3" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T3" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
+      <c r="A4" s="0">
+        <v>3</v>
+      </c>
       <c r="B4" s="0" t="s">
         <v>30</v>
       </c>
@@ -956,13 +965,13 @@
         <v>25</v>
       </c>
       <c r="S4" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T4" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
+      <c r="A5" s="0">
+        <v>4</v>
+      </c>
       <c r="B5" s="0" t="s">
         <v>32</v>
       </c>
@@ -976,7 +985,7 @@
         <v>21</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5" s="0">
         <v>30</v>
@@ -1013,13 +1022,13 @@
         <v>25</v>
       </c>
       <c r="S5" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T5" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
+      <c r="A6" s="0">
+        <v>5</v>
+      </c>
       <c r="B6" s="0" t="s">
         <v>33</v>
       </c>
@@ -1070,13 +1079,13 @@
         <v>25</v>
       </c>
       <c r="S6" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T6" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
+      <c r="A7" s="0">
+        <v>6</v>
+      </c>
       <c r="B7" s="0" t="s">
         <v>35</v>
       </c>
@@ -1090,7 +1099,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7" s="0">
         <v>190</v>
@@ -1127,13 +1136,13 @@
         <v>25</v>
       </c>
       <c r="S7" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T7" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
+      <c r="A8" s="0">
+        <v>7</v>
+      </c>
       <c r="B8" s="0" t="s">
         <v>36</v>
       </c>
@@ -1184,13 +1193,13 @@
         <v>25</v>
       </c>
       <c r="S8" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T8" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
+      <c r="A9" s="0">
+        <v>8</v>
+      </c>
       <c r="B9" s="0" t="s">
         <v>38</v>
       </c>
@@ -1204,7 +1213,7 @@
         <v>21</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G9" s="0">
         <v>180</v>
@@ -1241,13 +1250,13 @@
         <v>25</v>
       </c>
       <c r="S9" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T9" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
+      <c r="A10" s="0">
+        <v>9</v>
+      </c>
       <c r="B10" s="0" t="s">
         <v>39</v>
       </c>
@@ -1298,13 +1307,13 @@
         <v>25</v>
       </c>
       <c r="S10" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T10" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
+      <c r="A11" s="0">
+        <v>10</v>
+      </c>
       <c r="B11" s="0" t="s">
         <v>41</v>
       </c>
@@ -1318,7 +1327,7 @@
         <v>21</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11" s="0">
         <v>130</v>
@@ -1355,13 +1364,13 @@
         <v>25</v>
       </c>
       <c r="S11" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T11" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
+      <c r="A12" s="0">
+        <v>11</v>
+      </c>
       <c r="B12" s="0" t="s">
         <v>42</v>
       </c>
@@ -1412,13 +1421,13 @@
         <v>25</v>
       </c>
       <c r="S12" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T12" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
+      <c r="A13" s="0">
+        <v>12</v>
+      </c>
       <c r="B13" s="0" t="s">
         <v>44</v>
       </c>
@@ -1432,7 +1441,7 @@
         <v>21</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G13" s="0">
         <v>20</v>
@@ -1469,13 +1478,13 @@
         <v>25</v>
       </c>
       <c r="S13" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T13" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
+      <c r="A14" s="0">
+        <v>13</v>
+      </c>
       <c r="B14" s="0" t="s">
         <v>45</v>
       </c>
@@ -1526,13 +1535,13 @@
         <v>25</v>
       </c>
       <c r="S14" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T14" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
+      <c r="A15" s="0">
+        <v>14</v>
+      </c>
       <c r="B15" s="0" t="s">
         <v>47</v>
       </c>
@@ -1546,7 +1555,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G15" s="0">
         <v>140</v>
@@ -1583,13 +1592,13 @@
         <v>25</v>
       </c>
       <c r="S15" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
+      <c r="A16" s="0">
+        <v>15</v>
+      </c>
       <c r="B16" s="0" t="s">
         <v>48</v>
       </c>
@@ -1640,13 +1649,13 @@
         <v>25</v>
       </c>
       <c r="S16" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
+      <c r="A17" s="0">
+        <v>16</v>
+      </c>
       <c r="B17" s="0" t="s">
         <v>50</v>
       </c>
@@ -1660,7 +1669,7 @@
         <v>21</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G17" s="0">
         <v>10</v>
@@ -1697,13 +1706,13 @@
         <v>25</v>
       </c>
       <c r="S17" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T17" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
+      <c r="A18" s="0">
+        <v>17</v>
+      </c>
       <c r="B18" s="0" t="s">
         <v>51</v>
       </c>
@@ -1754,13 +1763,13 @@
         <v>25</v>
       </c>
       <c r="S18" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T18" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
+      <c r="A19" s="0">
+        <v>18</v>
+      </c>
       <c r="B19" s="0" t="s">
         <v>53</v>
       </c>
@@ -1774,7 +1783,7 @@
         <v>21</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19" s="0">
         <v>120</v>
@@ -1811,13 +1820,13 @@
         <v>25</v>
       </c>
       <c r="S19" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T19" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
+      <c r="A20" s="0">
+        <v>19</v>
+      </c>
       <c r="B20" s="0" t="s">
         <v>54</v>
       </c>
@@ -1868,13 +1877,13 @@
         <v>25</v>
       </c>
       <c r="S20" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T20" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
+      <c r="A21" s="0">
+        <v>20</v>
+      </c>
       <c r="B21" s="0" t="s">
         <v>56</v>
       </c>
@@ -1888,7 +1897,7 @@
         <v>21</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G21" s="0">
         <v>30</v>
@@ -1925,13 +1934,13 @@
         <v>57</v>
       </c>
       <c r="S21" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T21" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
+      <c r="A22" s="0">
+        <v>21</v>
+      </c>
       <c r="B22" s="0" t="s">
         <v>58</v>
       </c>
@@ -1982,13 +1991,13 @@
         <v>57</v>
       </c>
       <c r="S22" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T22" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
+      <c r="A23" s="0">
+        <v>22</v>
+      </c>
       <c r="B23" s="0" t="s">
         <v>60</v>
       </c>
@@ -2002,7 +2011,7 @@
         <v>59</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G23" s="0">
         <v>30</v>
@@ -2039,13 +2048,13 @@
         <v>57</v>
       </c>
       <c r="S23" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T23" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
+      <c r="A24" s="0">
+        <v>23</v>
+      </c>
       <c r="B24" s="0" t="s">
         <v>61</v>
       </c>
@@ -2096,13 +2105,13 @@
         <v>57</v>
       </c>
       <c r="S24" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T24" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25">
+      <c r="A25" s="0">
+        <v>24</v>
+      </c>
       <c r="B25" s="0" t="s">
         <v>63</v>
       </c>
@@ -2116,7 +2125,7 @@
         <v>59</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25" s="0">
         <v>150</v>
@@ -2153,13 +2162,13 @@
         <v>57</v>
       </c>
       <c r="S25" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T25" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26">
+      <c r="A26" s="0">
+        <v>25</v>
+      </c>
       <c r="B26" s="0" t="s">
         <v>64</v>
       </c>
@@ -2210,13 +2219,13 @@
         <v>57</v>
       </c>
       <c r="S26" s="0" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0">
         <v>26</v>
       </c>
-      <c r="T26" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
       <c r="B27" s="0" t="s">
         <v>66</v>
       </c>
@@ -2230,7 +2239,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G27" s="0">
         <v>120</v>
@@ -2267,13 +2276,13 @@
         <v>57</v>
       </c>
       <c r="S27" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T27" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28">
+      <c r="A28" s="0">
+        <v>27</v>
+      </c>
       <c r="B28" s="0" t="s">
         <v>68</v>
       </c>
@@ -2324,13 +2333,13 @@
         <v>57</v>
       </c>
       <c r="S28" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T28" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
+      <c r="A29" s="0">
+        <v>28</v>
+      </c>
       <c r="B29" s="0" t="s">
         <v>70</v>
       </c>
@@ -2381,13 +2390,13 @@
         <v>57</v>
       </c>
       <c r="S29" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T29" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30">
+      <c r="A30" s="0">
+        <v>29</v>
+      </c>
       <c r="B30" s="0" t="s">
         <v>19</v>
       </c>
@@ -2438,15 +2447,15 @@
         <v>73</v>
       </c>
       <c r="S30" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0">
+        <v>30</v>
+      </c>
+      <c r="B31" s="0" t="s">
         <v>26</v>
-      </c>
-      <c r="T30" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="0" t="s">
-        <v>27</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>71</v>
@@ -2458,7 +2467,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G31" s="0">
         <v>280</v>
@@ -2495,13 +2504,13 @@
         <v>73</v>
       </c>
       <c r="S31" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T31" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32">
+      <c r="A32" s="0">
+        <v>31</v>
+      </c>
       <c r="B32" s="0" t="s">
         <v>75</v>
       </c>
@@ -2552,13 +2561,13 @@
         <v>73</v>
       </c>
       <c r="S32" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T32" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33">
+      <c r="A33" s="0">
+        <v>32</v>
+      </c>
       <c r="B33" s="0" t="s">
         <v>77</v>
       </c>
@@ -2572,7 +2581,7 @@
         <v>59</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G33" s="0">
         <v>70</v>
@@ -2609,13 +2618,13 @@
         <v>73</v>
       </c>
       <c r="S33" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T33" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34">
+      <c r="A34" s="0">
+        <v>33</v>
+      </c>
       <c r="B34" s="0" t="s">
         <v>78</v>
       </c>
@@ -2666,13 +2675,13 @@
         <v>73</v>
       </c>
       <c r="S34" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T34" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35">
+      <c r="A35" s="0">
+        <v>34</v>
+      </c>
       <c r="B35" s="0" t="s">
         <v>79</v>
       </c>
@@ -2723,13 +2732,13 @@
         <v>73</v>
       </c>
       <c r="S35" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T35" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36">
+      <c r="A36" s="0">
+        <v>35</v>
+      </c>
       <c r="B36" s="0" t="s">
         <v>81</v>
       </c>
@@ -2780,13 +2789,13 @@
         <v>73</v>
       </c>
       <c r="S36" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T36" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37">
+      <c r="A37" s="0">
+        <v>36</v>
+      </c>
       <c r="B37" s="0" t="s">
         <v>30</v>
       </c>
@@ -2837,13 +2846,13 @@
         <v>85</v>
       </c>
       <c r="S37" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T37" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
+      <c r="A38" s="0">
+        <v>37</v>
+      </c>
       <c r="B38" s="0" t="s">
         <v>32</v>
       </c>
@@ -2857,7 +2866,7 @@
         <v>21</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G38" s="0">
         <v>10</v>
@@ -2894,13 +2903,13 @@
         <v>85</v>
       </c>
       <c r="S38" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T38" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39">
+      <c r="A39" s="0">
+        <v>38</v>
+      </c>
       <c r="B39" s="0" t="s">
         <v>33</v>
       </c>
@@ -2951,13 +2960,13 @@
         <v>85</v>
       </c>
       <c r="S39" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T39" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40">
+      <c r="A40" s="0">
+        <v>39</v>
+      </c>
       <c r="B40" s="0" t="s">
         <v>35</v>
       </c>
@@ -2971,7 +2980,7 @@
         <v>21</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G40" s="0">
         <v>30</v>
@@ -3008,13 +3017,13 @@
         <v>85</v>
       </c>
       <c r="S40" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T40" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41">
+      <c r="A41" s="0">
+        <v>40</v>
+      </c>
       <c r="B41" s="0" t="s">
         <v>36</v>
       </c>
@@ -3065,13 +3074,13 @@
         <v>85</v>
       </c>
       <c r="S41" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T41" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42">
+      <c r="A42" s="0">
+        <v>41</v>
+      </c>
       <c r="B42" s="0" t="s">
         <v>38</v>
       </c>
@@ -3085,7 +3094,7 @@
         <v>21</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G42" s="0">
         <v>90</v>
@@ -3122,13 +3131,13 @@
         <v>85</v>
       </c>
       <c r="S42" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T42" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43">
+      <c r="A43" s="0">
+        <v>42</v>
+      </c>
       <c r="B43" s="0" t="s">
         <v>39</v>
       </c>
@@ -3179,13 +3188,13 @@
         <v>85</v>
       </c>
       <c r="S43" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T43" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44">
+      <c r="A44" s="0">
+        <v>43</v>
+      </c>
       <c r="B44" s="0" t="s">
         <v>41</v>
       </c>
@@ -3199,7 +3208,7 @@
         <v>21</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G44" s="0">
         <v>70</v>
@@ -3236,13 +3245,13 @@
         <v>85</v>
       </c>
       <c r="S44" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T44" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45">
+      <c r="A45" s="0">
+        <v>44</v>
+      </c>
       <c r="B45" s="0" t="s">
         <v>45</v>
       </c>
@@ -3293,13 +3302,13 @@
         <v>85</v>
       </c>
       <c r="S45" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T45" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46">
+      <c r="A46" s="0">
+        <v>45</v>
+      </c>
       <c r="B46" s="0" t="s">
         <v>47</v>
       </c>
@@ -3313,7 +3322,7 @@
         <v>21</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G46" s="0">
         <v>60</v>
@@ -3350,13 +3359,13 @@
         <v>85</v>
       </c>
       <c r="S46" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T46" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47">
+      <c r="A47" s="0">
+        <v>46</v>
+      </c>
       <c r="B47" s="0" t="s">
         <v>51</v>
       </c>
@@ -3407,13 +3416,13 @@
         <v>85</v>
       </c>
       <c r="S47" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T47" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48">
+      <c r="A48" s="0">
+        <v>47</v>
+      </c>
       <c r="B48" s="0" t="s">
         <v>53</v>
       </c>
@@ -3427,7 +3436,7 @@
         <v>21</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G48" s="0">
         <v>20</v>
@@ -3464,13 +3473,13 @@
         <v>85</v>
       </c>
       <c r="S48" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T48" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49">
+      <c r="A49" s="0">
+        <v>48</v>
+      </c>
       <c r="B49" s="0" t="s">
         <v>54</v>
       </c>
@@ -3521,13 +3530,13 @@
         <v>85</v>
       </c>
       <c r="S49" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T49" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50">
+      <c r="A50" s="0">
+        <v>49</v>
+      </c>
       <c r="B50" s="0" t="s">
         <v>56</v>
       </c>
@@ -3541,7 +3550,7 @@
         <v>21</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G50" s="0">
         <v>10</v>
@@ -3578,13 +3587,13 @@
         <v>85</v>
       </c>
       <c r="S50" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T50" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51">
+      <c r="A51" s="0">
+        <v>50</v>
+      </c>
       <c r="B51" s="0" t="s">
         <v>58</v>
       </c>
@@ -3635,13 +3644,13 @@
         <v>85</v>
       </c>
       <c r="S51" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T51" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52">
+      <c r="A52" s="0">
+        <v>51</v>
+      </c>
       <c r="B52" s="0" t="s">
         <v>60</v>
       </c>
@@ -3655,7 +3664,7 @@
         <v>59</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G52" s="0">
         <v>20</v>
@@ -3692,13 +3701,13 @@
         <v>85</v>
       </c>
       <c r="S52" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T52" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53">
+      <c r="A53" s="0">
+        <v>52</v>
+      </c>
       <c r="B53" s="0" t="s">
         <v>61</v>
       </c>
@@ -3749,13 +3758,13 @@
         <v>85</v>
       </c>
       <c r="S53" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T53" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54">
+      <c r="A54" s="0">
+        <v>53</v>
+      </c>
       <c r="B54" s="0" t="s">
         <v>63</v>
       </c>
@@ -3769,7 +3778,7 @@
         <v>59</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G54" s="0">
         <v>10</v>
@@ -3806,13 +3815,13 @@
         <v>85</v>
       </c>
       <c r="S54" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T54" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="55">
+      <c r="A55" s="0">
+        <v>54</v>
+      </c>
       <c r="B55" s="0" t="s">
         <v>36</v>
       </c>
@@ -3863,13 +3872,13 @@
         <v>95</v>
       </c>
       <c r="S55" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T55" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
+      <c r="A56" s="0">
+        <v>55</v>
+      </c>
       <c r="B56" s="0" t="s">
         <v>38</v>
       </c>
@@ -3883,7 +3892,7 @@
         <v>21</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G56" s="0">
         <v>10</v>
@@ -3920,13 +3929,13 @@
         <v>95</v>
       </c>
       <c r="S56" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T56" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="57">
+      <c r="A57" s="0">
+        <v>56</v>
+      </c>
       <c r="B57" s="0" t="s">
         <v>45</v>
       </c>
@@ -3977,13 +3986,13 @@
         <v>95</v>
       </c>
       <c r="S57" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T57" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58">
+      <c r="A58" s="0">
+        <v>57</v>
+      </c>
       <c r="B58" s="0" t="s">
         <v>47</v>
       </c>
@@ -3997,7 +4006,7 @@
         <v>21</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G58" s="0">
         <v>10</v>
@@ -4034,13 +4043,13 @@
         <v>95</v>
       </c>
       <c r="S58" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T58" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59">
+      <c r="A59" s="0">
+        <v>58</v>
+      </c>
       <c r="B59" s="0" t="s">
         <v>51</v>
       </c>
@@ -4091,13 +4100,13 @@
         <v>95</v>
       </c>
       <c r="S59" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T59" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="60">
+      <c r="A60" s="0">
+        <v>59</v>
+      </c>
       <c r="B60" s="0" t="s">
         <v>53</v>
       </c>
@@ -4111,7 +4120,7 @@
         <v>21</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G60" s="0">
         <v>10</v>
@@ -4148,13 +4157,13 @@
         <v>95</v>
       </c>
       <c r="S60" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T60" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61">
+      <c r="A61" s="0">
+        <v>60</v>
+      </c>
       <c r="B61" s="0" t="s">
         <v>36</v>
       </c>
@@ -4205,13 +4214,13 @@
         <v>100</v>
       </c>
       <c r="S61" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T61" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62">
+      <c r="A62" s="0">
+        <v>61</v>
+      </c>
       <c r="B62" s="0" t="s">
         <v>38</v>
       </c>
@@ -4225,7 +4234,7 @@
         <v>21</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G62" s="0">
         <v>40</v>
@@ -4262,13 +4271,13 @@
         <v>100</v>
       </c>
       <c r="S62" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T62" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63">
+      <c r="A63" s="0">
+        <v>62</v>
+      </c>
       <c r="B63" s="0" t="s">
         <v>45</v>
       </c>
@@ -4319,13 +4328,13 @@
         <v>100</v>
       </c>
       <c r="S63" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T63" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="64">
+      <c r="A64" s="0">
+        <v>63</v>
+      </c>
       <c r="B64" s="0" t="s">
         <v>47</v>
       </c>
@@ -4339,7 +4348,7 @@
         <v>21</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G64" s="0">
         <v>20</v>
@@ -4376,13 +4385,13 @@
         <v>100</v>
       </c>
       <c r="S64" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T64" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65">
+      <c r="A65" s="0">
+        <v>64</v>
+      </c>
       <c r="B65" s="0" t="s">
         <v>51</v>
       </c>
@@ -4433,13 +4442,13 @@
         <v>100</v>
       </c>
       <c r="S65" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T65" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66">
+      <c r="A66" s="0">
+        <v>65</v>
+      </c>
       <c r="B66" s="0" t="s">
         <v>53</v>
       </c>
@@ -4453,7 +4462,7 @@
         <v>21</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G66" s="0">
         <v>20</v>
@@ -4490,13 +4499,13 @@
         <v>100</v>
       </c>
       <c r="S66" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T66" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67">
+      <c r="A67" s="0">
+        <v>66</v>
+      </c>
       <c r="B67" s="0" t="s">
         <v>102</v>
       </c>
@@ -4547,13 +4556,13 @@
         <v>100</v>
       </c>
       <c r="S67" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T67" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68">
+      <c r="A68" s="0">
+        <v>67</v>
+      </c>
       <c r="B68" s="0" t="s">
         <v>19</v>
       </c>
@@ -4604,15 +4613,15 @@
         <v>106</v>
       </c>
       <c r="S68" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0">
+        <v>68</v>
+      </c>
+      <c r="B69" s="0" t="s">
         <v>26</v>
-      </c>
-      <c r="T68" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="0" t="s">
-        <v>27</v>
       </c>
       <c r="C69" s="0" t="s">
         <v>104</v>
@@ -4624,7 +4633,7 @@
         <v>21</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G69" s="0">
         <v>400</v>
@@ -4661,13 +4670,13 @@
         <v>106</v>
       </c>
       <c r="S69" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T69" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="70">
+      <c r="A70" s="0">
+        <v>69</v>
+      </c>
       <c r="B70" s="0" t="s">
         <v>30</v>
       </c>
@@ -4718,13 +4727,13 @@
         <v>106</v>
       </c>
       <c r="S70" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T70" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="71">
+      <c r="A71" s="0">
+        <v>70</v>
+      </c>
       <c r="B71" s="0" t="s">
         <v>32</v>
       </c>
@@ -4738,7 +4747,7 @@
         <v>21</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G71" s="0">
         <v>90</v>
@@ -4775,13 +4784,13 @@
         <v>106</v>
       </c>
       <c r="S71" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T71" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="72">
+      <c r="A72" s="0">
+        <v>71</v>
+      </c>
       <c r="B72" s="0" t="s">
         <v>33</v>
       </c>
@@ -4832,13 +4841,13 @@
         <v>106</v>
       </c>
       <c r="S72" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T72" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="73">
+      <c r="A73" s="0">
+        <v>72</v>
+      </c>
       <c r="B73" s="0" t="s">
         <v>35</v>
       </c>
@@ -4852,7 +4861,7 @@
         <v>21</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G73" s="0">
         <v>340</v>
@@ -4889,13 +4898,13 @@
         <v>106</v>
       </c>
       <c r="S73" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T73" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74">
+      <c r="A74" s="0">
+        <v>73</v>
+      </c>
       <c r="B74" s="0" t="s">
         <v>36</v>
       </c>
@@ -4946,13 +4955,13 @@
         <v>106</v>
       </c>
       <c r="S74" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T74" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="75">
+      <c r="A75" s="0">
+        <v>74</v>
+      </c>
       <c r="B75" s="0" t="s">
         <v>38</v>
       </c>
@@ -4966,7 +4975,7 @@
         <v>21</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G75" s="0">
         <v>390</v>
@@ -5003,13 +5012,13 @@
         <v>106</v>
       </c>
       <c r="S75" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T75" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="76">
+      <c r="A76" s="0">
+        <v>75</v>
+      </c>
       <c r="B76" s="0" t="s">
         <v>39</v>
       </c>
@@ -5060,13 +5069,13 @@
         <v>106</v>
       </c>
       <c r="S76" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T76" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77">
+      <c r="A77" s="0">
+        <v>76</v>
+      </c>
       <c r="B77" s="0" t="s">
         <v>41</v>
       </c>
@@ -5080,7 +5089,7 @@
         <v>21</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G77" s="0">
         <v>380</v>
@@ -5117,13 +5126,13 @@
         <v>109</v>
       </c>
       <c r="S77" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T77" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78">
+      <c r="A78" s="0">
+        <v>77</v>
+      </c>
       <c r="B78" s="0" t="s">
         <v>45</v>
       </c>
@@ -5174,13 +5183,13 @@
         <v>109</v>
       </c>
       <c r="S78" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T78" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="79">
+      <c r="A79" s="0">
+        <v>78</v>
+      </c>
       <c r="B79" s="0" t="s">
         <v>47</v>
       </c>
@@ -5194,7 +5203,7 @@
         <v>21</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G79" s="0">
         <v>330</v>
@@ -5231,13 +5240,13 @@
         <v>109</v>
       </c>
       <c r="S79" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T79" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80">
+      <c r="A80" s="0">
+        <v>79</v>
+      </c>
       <c r="B80" s="0" t="s">
         <v>51</v>
       </c>
@@ -5288,13 +5297,13 @@
         <v>109</v>
       </c>
       <c r="S80" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T80" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="81">
+      <c r="A81" s="0">
+        <v>80</v>
+      </c>
       <c r="B81" s="0" t="s">
         <v>53</v>
       </c>
@@ -5308,7 +5317,7 @@
         <v>21</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G81" s="0">
         <v>50</v>
@@ -5345,13 +5354,13 @@
         <v>109</v>
       </c>
       <c r="S81" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T81" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="82">
+      <c r="A82" s="0">
+        <v>81</v>
+      </c>
       <c r="B82" s="0" t="s">
         <v>54</v>
       </c>
@@ -5402,13 +5411,13 @@
         <v>109</v>
       </c>
       <c r="S82" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T82" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83">
+      <c r="A83" s="0">
+        <v>82</v>
+      </c>
       <c r="B83" s="0" t="s">
         <v>56</v>
       </c>
@@ -5422,7 +5431,7 @@
         <v>21</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G83" s="0">
         <v>70</v>
@@ -5459,13 +5468,13 @@
         <v>109</v>
       </c>
       <c r="S83" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T83" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="84">
+      <c r="A84" s="0">
+        <v>83</v>
+      </c>
       <c r="B84" s="0" t="s">
         <v>58</v>
       </c>
@@ -5516,13 +5525,13 @@
         <v>109</v>
       </c>
       <c r="S84" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T84" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85">
+      <c r="A85" s="0">
+        <v>84</v>
+      </c>
       <c r="B85" s="0" t="s">
         <v>60</v>
       </c>
@@ -5536,7 +5545,7 @@
         <v>59</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G85" s="0">
         <v>80</v>
@@ -5573,13 +5582,13 @@
         <v>109</v>
       </c>
       <c r="S85" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T85" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86">
+      <c r="A86" s="0">
+        <v>85</v>
+      </c>
       <c r="B86" s="0" t="s">
         <v>61</v>
       </c>
@@ -5630,13 +5639,13 @@
         <v>109</v>
       </c>
       <c r="S86" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T86" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87">
+      <c r="A87" s="0">
+        <v>86</v>
+      </c>
       <c r="B87" s="0" t="s">
         <v>63</v>
       </c>
@@ -5650,7 +5659,7 @@
         <v>59</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G87" s="0">
         <v>230</v>
@@ -5687,13 +5696,13 @@
         <v>109</v>
       </c>
       <c r="S87" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T87" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="88">
+      <c r="A88" s="0">
+        <v>87</v>
+      </c>
       <c r="B88" s="0" t="s">
         <v>64</v>
       </c>
@@ -5744,13 +5753,13 @@
         <v>109</v>
       </c>
       <c r="S88" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T88" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="89">
+      <c r="A89" s="0">
+        <v>88</v>
+      </c>
       <c r="B89" s="0" t="s">
         <v>66</v>
       </c>
@@ -5764,7 +5773,7 @@
         <v>21</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G89" s="0">
         <v>70</v>
@@ -5801,13 +5810,13 @@
         <v>109</v>
       </c>
       <c r="S89" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T89" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="90">
+      <c r="A90" s="0">
+        <v>89</v>
+      </c>
       <c r="B90" s="0" t="s">
         <v>68</v>
       </c>
@@ -5858,13 +5867,13 @@
         <v>109</v>
       </c>
       <c r="S90" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T90" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="91">
+      <c r="A91" s="0">
+        <v>90</v>
+      </c>
       <c r="B91" s="0" t="s">
         <v>111</v>
       </c>
@@ -5915,13 +5924,13 @@
         <v>109</v>
       </c>
       <c r="S91" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T91" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="92">
+      <c r="A92" s="0">
+        <v>91</v>
+      </c>
       <c r="B92" s="0" t="s">
         <v>112</v>
       </c>
@@ -5935,7 +5944,7 @@
         <v>21</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G92" s="0">
         <v>70</v>
@@ -5972,13 +5981,13 @@
         <v>109</v>
       </c>
       <c r="S92" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T92" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="93">
+      <c r="A93" s="0">
+        <v>92</v>
+      </c>
       <c r="B93" s="0" t="s">
         <v>113</v>
       </c>
@@ -6029,13 +6038,13 @@
         <v>109</v>
       </c>
       <c r="S93" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T93" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="94">
+      <c r="A94" s="0">
+        <v>93</v>
+      </c>
       <c r="B94" s="0" t="s">
         <v>19</v>
       </c>
@@ -6086,15 +6095,15 @@
         <v>116</v>
       </c>
       <c r="S94" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0">
+        <v>94</v>
+      </c>
+      <c r="B95" s="0" t="s">
         <v>26</v>
-      </c>
-      <c r="T94" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="0" t="s">
-        <v>27</v>
       </c>
       <c r="C95" s="0" t="s">
         <v>114</v>
@@ -6106,7 +6115,7 @@
         <v>21</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G95" s="0">
         <v>470</v>
@@ -6143,13 +6152,13 @@
         <v>116</v>
       </c>
       <c r="S95" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T95" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="96">
+      <c r="A96" s="0">
+        <v>95</v>
+      </c>
       <c r="B96" s="0" t="s">
         <v>30</v>
       </c>
@@ -6200,13 +6209,13 @@
         <v>116</v>
       </c>
       <c r="S96" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T96" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97">
+      <c r="A97" s="0">
+        <v>96</v>
+      </c>
       <c r="B97" s="0" t="s">
         <v>32</v>
       </c>
@@ -6220,7 +6229,7 @@
         <v>21</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G97" s="0">
         <v>60</v>
@@ -6257,13 +6266,13 @@
         <v>116</v>
       </c>
       <c r="S97" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T97" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="98">
+      <c r="A98" s="0">
+        <v>97</v>
+      </c>
       <c r="B98" s="0" t="s">
         <v>33</v>
       </c>
@@ -6314,13 +6323,13 @@
         <v>116</v>
       </c>
       <c r="S98" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T98" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="99">
+      <c r="A99" s="0">
+        <v>98</v>
+      </c>
       <c r="B99" s="0" t="s">
         <v>35</v>
       </c>
@@ -6334,7 +6343,7 @@
         <v>21</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G99" s="0">
         <v>170</v>
@@ -6371,13 +6380,13 @@
         <v>116</v>
       </c>
       <c r="S99" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T99" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="100">
+      <c r="A100" s="0">
+        <v>99</v>
+      </c>
       <c r="B100" s="0" t="s">
         <v>36</v>
       </c>
@@ -6428,13 +6437,13 @@
         <v>116</v>
       </c>
       <c r="S100" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T100" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="101">
+      <c r="A101" s="0">
+        <v>100</v>
+      </c>
       <c r="B101" s="0" t="s">
         <v>38</v>
       </c>
@@ -6448,7 +6457,7 @@
         <v>21</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G101" s="0">
         <v>230</v>
@@ -6485,13 +6494,13 @@
         <v>116</v>
       </c>
       <c r="S101" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T101" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="102">
+      <c r="A102" s="0">
+        <v>101</v>
+      </c>
       <c r="B102" s="0" t="s">
         <v>39</v>
       </c>
@@ -6542,13 +6551,13 @@
         <v>116</v>
       </c>
       <c r="S102" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T102" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103">
+      <c r="A103" s="0">
+        <v>102</v>
+      </c>
       <c r="B103" s="0" t="s">
         <v>41</v>
       </c>
@@ -6562,7 +6571,7 @@
         <v>21</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G103" s="0">
         <v>220</v>
@@ -6599,13 +6608,13 @@
         <v>116</v>
       </c>
       <c r="S103" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T103" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104">
+      <c r="A104" s="0">
+        <v>103</v>
+      </c>
       <c r="B104" s="0" t="s">
         <v>45</v>
       </c>
@@ -6656,13 +6665,13 @@
         <v>116</v>
       </c>
       <c r="S104" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T104" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="105">
+      <c r="A105" s="0">
+        <v>104</v>
+      </c>
       <c r="B105" s="0" t="s">
         <v>47</v>
       </c>
@@ -6676,7 +6685,7 @@
         <v>21</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G105" s="0">
         <v>200</v>
@@ -6713,13 +6722,13 @@
         <v>116</v>
       </c>
       <c r="S105" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T105" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="106">
+      <c r="A106" s="0">
+        <v>105</v>
+      </c>
       <c r="B106" s="0" t="s">
         <v>51</v>
       </c>
@@ -6770,13 +6779,13 @@
         <v>116</v>
       </c>
       <c r="S106" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T106" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="107">
+      <c r="A107" s="0">
+        <v>106</v>
+      </c>
       <c r="B107" s="0" t="s">
         <v>53</v>
       </c>
@@ -6790,7 +6799,7 @@
         <v>21</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G107" s="0">
         <v>50</v>
@@ -6827,13 +6836,13 @@
         <v>116</v>
       </c>
       <c r="S107" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T107" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="108">
+      <c r="A108" s="0">
+        <v>107</v>
+      </c>
       <c r="B108" s="0" t="s">
         <v>58</v>
       </c>
@@ -6884,13 +6893,13 @@
         <v>116</v>
       </c>
       <c r="S108" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T108" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="109">
+      <c r="A109" s="0">
+        <v>108</v>
+      </c>
       <c r="B109" s="0" t="s">
         <v>60</v>
       </c>
@@ -6904,7 +6913,7 @@
         <v>59</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G109" s="0">
         <v>80</v>
@@ -6941,13 +6950,13 @@
         <v>124</v>
       </c>
       <c r="S109" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T109" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="110">
+      <c r="A110" s="0">
+        <v>109</v>
+      </c>
       <c r="B110" s="0" t="s">
         <v>61</v>
       </c>
@@ -6998,13 +7007,13 @@
         <v>124</v>
       </c>
       <c r="S110" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T110" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="111">
+      <c r="A111" s="0">
+        <v>110</v>
+      </c>
       <c r="B111" s="0" t="s">
         <v>63</v>
       </c>
@@ -7018,7 +7027,7 @@
         <v>59</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G111" s="0">
         <v>140</v>
@@ -7055,13 +7064,13 @@
         <v>124</v>
       </c>
       <c r="S111" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T111" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="112">
+      <c r="A112" s="0">
+        <v>111</v>
+      </c>
       <c r="B112" s="0" t="s">
         <v>64</v>
       </c>
@@ -7112,13 +7121,13 @@
         <v>124</v>
       </c>
       <c r="S112" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T112" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="113">
+      <c r="A113" s="0">
+        <v>112</v>
+      </c>
       <c r="B113" s="0" t="s">
         <v>66</v>
       </c>
@@ -7132,7 +7141,7 @@
         <v>21</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G113" s="0">
         <v>130</v>
@@ -7169,13 +7178,13 @@
         <v>124</v>
       </c>
       <c r="S113" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T113" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="114">
+      <c r="A114" s="0">
+        <v>113</v>
+      </c>
       <c r="B114" s="0" t="s">
         <v>68</v>
       </c>
@@ -7226,13 +7235,13 @@
         <v>124</v>
       </c>
       <c r="S114" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T114" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="115">
+      <c r="A115" s="0">
+        <v>114</v>
+      </c>
       <c r="B115" s="0" t="s">
         <v>111</v>
       </c>
@@ -7283,13 +7292,13 @@
         <v>124</v>
       </c>
       <c r="S115" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T115" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="116">
+      <c r="A116" s="0">
+        <v>115</v>
+      </c>
       <c r="B116" s="0" t="s">
         <v>112</v>
       </c>
@@ -7303,7 +7312,7 @@
         <v>21</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G116" s="0">
         <v>70</v>
@@ -7340,13 +7349,13 @@
         <v>124</v>
       </c>
       <c r="S116" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T116" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="117">
+      <c r="A117" s="0">
+        <v>116</v>
+      </c>
       <c r="B117" s="0" t="s">
         <v>113</v>
       </c>
@@ -7397,13 +7406,13 @@
         <v>124</v>
       </c>
       <c r="S117" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T117" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="118">
+      <c r="A118" s="0">
+        <v>117</v>
+      </c>
       <c r="B118" s="0" t="s">
         <v>36</v>
       </c>
@@ -7454,13 +7463,13 @@
         <v>128</v>
       </c>
       <c r="S118" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T118" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="119">
+      <c r="A119" s="0">
+        <v>118</v>
+      </c>
       <c r="B119" s="0" t="s">
         <v>38</v>
       </c>
@@ -7474,7 +7483,7 @@
         <v>21</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G119" s="0">
         <v>70</v>
@@ -7511,13 +7520,13 @@
         <v>128</v>
       </c>
       <c r="S119" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T119" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="120">
+      <c r="A120" s="0">
+        <v>119</v>
+      </c>
       <c r="B120" s="0" t="s">
         <v>45</v>
       </c>
@@ -7568,13 +7577,13 @@
         <v>128</v>
       </c>
       <c r="S120" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T120" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="121">
+      <c r="A121" s="0">
+        <v>120</v>
+      </c>
       <c r="B121" s="0" t="s">
         <v>47</v>
       </c>
@@ -7588,7 +7597,7 @@
         <v>21</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G121" s="0">
         <v>100</v>
@@ -7625,13 +7634,13 @@
         <v>128</v>
       </c>
       <c r="S121" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T121" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="122">
+      <c r="A122" s="0">
+        <v>121</v>
+      </c>
       <c r="B122" s="0" t="s">
         <v>58</v>
       </c>
@@ -7682,13 +7691,13 @@
         <v>128</v>
       </c>
       <c r="S122" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T122" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="123">
+      <c r="A123" s="0">
+        <v>122</v>
+      </c>
       <c r="B123" s="0" t="s">
         <v>60</v>
       </c>
@@ -7702,7 +7711,7 @@
         <v>59</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G123" s="0">
         <v>20</v>
@@ -7739,13 +7748,13 @@
         <v>128</v>
       </c>
       <c r="S123" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T123" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="124">
+      <c r="A124" s="0">
+        <v>123</v>
+      </c>
       <c r="B124" s="0" t="s">
         <v>61</v>
       </c>
@@ -7796,13 +7805,13 @@
         <v>128</v>
       </c>
       <c r="S124" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T124" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="125">
+      <c r="A125" s="0">
+        <v>124</v>
+      </c>
       <c r="B125" s="0" t="s">
         <v>63</v>
       </c>
@@ -7816,7 +7825,7 @@
         <v>59</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G125" s="0">
         <v>10</v>
@@ -7853,13 +7862,13 @@
         <v>128</v>
       </c>
       <c r="S125" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T125" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="126">
+      <c r="A126" s="0">
+        <v>125</v>
+      </c>
       <c r="B126" s="0" t="s">
         <v>30</v>
       </c>
@@ -7910,13 +7919,13 @@
         <v>131</v>
       </c>
       <c r="S126" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T126" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="127">
+      <c r="A127" s="0">
+        <v>126</v>
+      </c>
       <c r="B127" s="0" t="s">
         <v>32</v>
       </c>
@@ -7930,7 +7939,7 @@
         <v>21</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G127" s="0">
         <v>10</v>
@@ -7967,13 +7976,13 @@
         <v>131</v>
       </c>
       <c r="S127" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T127" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="128">
+      <c r="A128" s="0">
+        <v>127</v>
+      </c>
       <c r="B128" s="0" t="s">
         <v>36</v>
       </c>
@@ -8024,13 +8033,13 @@
         <v>131</v>
       </c>
       <c r="S128" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T128" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="129">
+      <c r="A129" s="0">
+        <v>128</v>
+      </c>
       <c r="B129" s="0" t="s">
         <v>38</v>
       </c>
@@ -8044,7 +8053,7 @@
         <v>21</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G129" s="0">
         <v>30</v>
@@ -8081,13 +8090,13 @@
         <v>131</v>
       </c>
       <c r="S129" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T129" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="130">
+      <c r="A130" s="0">
+        <v>129</v>
+      </c>
       <c r="B130" s="0" t="s">
         <v>45</v>
       </c>
@@ -8138,13 +8147,13 @@
         <v>131</v>
       </c>
       <c r="S130" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T130" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="131">
+      <c r="A131" s="0">
+        <v>130</v>
+      </c>
       <c r="B131" s="0" t="s">
         <v>47</v>
       </c>
@@ -8158,7 +8167,7 @@
         <v>21</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G131" s="0">
         <v>40</v>
@@ -8195,13 +8204,13 @@
         <v>131</v>
       </c>
       <c r="S131" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T131" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="132">
+      <c r="A132" s="0">
+        <v>131</v>
+      </c>
       <c r="B132" s="0" t="s">
         <v>30</v>
       </c>
@@ -8252,13 +8261,13 @@
         <v>135</v>
       </c>
       <c r="S132" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T132" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="133">
+      <c r="A133" s="0">
+        <v>132</v>
+      </c>
       <c r="B133" s="0" t="s">
         <v>32</v>
       </c>
@@ -8272,7 +8281,7 @@
         <v>21</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G133" s="0">
         <v>30</v>
@@ -8309,13 +8318,13 @@
         <v>135</v>
       </c>
       <c r="S133" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T133" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="134">
+      <c r="A134" s="0">
+        <v>133</v>
+      </c>
       <c r="B134" s="0" t="s">
         <v>36</v>
       </c>
@@ -8366,13 +8375,13 @@
         <v>135</v>
       </c>
       <c r="S134" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T134" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="135">
+      <c r="A135" s="0">
+        <v>134</v>
+      </c>
       <c r="B135" s="0" t="s">
         <v>38</v>
       </c>
@@ -8386,7 +8395,7 @@
         <v>21</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G135" s="0">
         <v>100</v>
@@ -8423,13 +8432,13 @@
         <v>135</v>
       </c>
       <c r="S135" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T135" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="136">
+      <c r="A136" s="0">
+        <v>135</v>
+      </c>
       <c r="B136" s="0" t="s">
         <v>36</v>
       </c>
@@ -8480,13 +8489,13 @@
         <v>139</v>
       </c>
       <c r="S136" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T136" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="137">
+      <c r="A137" s="0">
+        <v>136</v>
+      </c>
       <c r="B137" s="0" t="s">
         <v>38</v>
       </c>
@@ -8500,7 +8509,7 @@
         <v>21</v>
       </c>
       <c r="F137" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G137" s="0">
         <v>50</v>
@@ -8537,13 +8546,13 @@
         <v>139</v>
       </c>
       <c r="S137" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T137" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="138">
+      <c r="A138" s="0">
+        <v>137</v>
+      </c>
       <c r="B138" s="0" t="s">
         <v>45</v>
       </c>
@@ -8594,13 +8603,13 @@
         <v>139</v>
       </c>
       <c r="S138" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T138" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="139">
+      <c r="A139" s="0">
+        <v>138</v>
+      </c>
       <c r="B139" s="0" t="s">
         <v>47</v>
       </c>
@@ -8614,7 +8623,7 @@
         <v>21</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G139" s="0">
         <v>70</v>
@@ -8651,13 +8660,13 @@
         <v>139</v>
       </c>
       <c r="S139" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T139" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="140">
+      <c r="A140" s="0">
+        <v>139</v>
+      </c>
       <c r="B140" s="0" t="s">
         <v>58</v>
       </c>
@@ -8708,13 +8717,13 @@
         <v>139</v>
       </c>
       <c r="S140" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T140" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="141">
+      <c r="A141" s="0">
+        <v>140</v>
+      </c>
       <c r="B141" s="0" t="s">
         <v>60</v>
       </c>
@@ -8728,7 +8737,7 @@
         <v>59</v>
       </c>
       <c r="F141" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G141" s="0">
         <v>10</v>
@@ -8765,13 +8774,13 @@
         <v>139</v>
       </c>
       <c r="S141" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T141" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="142">
+      <c r="A142" s="0">
+        <v>141</v>
+      </c>
       <c r="B142" s="0" t="s">
         <v>141</v>
       </c>
@@ -8822,13 +8831,13 @@
         <v>144</v>
       </c>
       <c r="S142" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T142" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="143">
+      <c r="A143" s="0">
+        <v>142</v>
+      </c>
       <c r="B143" s="0" t="s">
         <v>145</v>
       </c>
@@ -8879,13 +8888,13 @@
         <v>144</v>
       </c>
       <c r="S143" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T143" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="144">
+      <c r="A144" s="0">
+        <v>143</v>
+      </c>
       <c r="B144" s="0" t="s">
         <v>146</v>
       </c>
@@ -8936,13 +8945,13 @@
         <v>144</v>
       </c>
       <c r="S144" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T144" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="145">
+      <c r="A145" s="0">
+        <v>144</v>
+      </c>
       <c r="B145" s="0" t="s">
         <v>147</v>
       </c>
@@ -8993,13 +9002,13 @@
         <v>144</v>
       </c>
       <c r="S145" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T145" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="146">
+      <c r="A146" s="0">
+        <v>145</v>
+      </c>
       <c r="B146" s="0" t="s">
         <v>148</v>
       </c>
@@ -9050,13 +9059,13 @@
         <v>144</v>
       </c>
       <c r="S146" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T146" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="147">
+      <c r="A147" s="0">
+        <v>146</v>
+      </c>
       <c r="B147" s="0" t="s">
         <v>149</v>
       </c>
@@ -9107,13 +9116,13 @@
         <v>144</v>
       </c>
       <c r="S147" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T147" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="148">
+      <c r="A148" s="0">
+        <v>147</v>
+      </c>
       <c r="B148" s="0" t="s">
         <v>151</v>
       </c>
@@ -9164,13 +9173,13 @@
         <v>144</v>
       </c>
       <c r="S148" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T148" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="149">
+      <c r="A149" s="0">
+        <v>148</v>
+      </c>
       <c r="B149" s="0" t="s">
         <v>153</v>
       </c>
@@ -9221,13 +9230,13 @@
         <v>144</v>
       </c>
       <c r="S149" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T149" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="150">
+      <c r="A150" s="0">
+        <v>149</v>
+      </c>
       <c r="B150" s="0" t="s">
         <v>154</v>
       </c>
@@ -9278,13 +9287,13 @@
         <v>144</v>
       </c>
       <c r="S150" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T150" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="151">
+      <c r="A151" s="0">
+        <v>150</v>
+      </c>
       <c r="B151" s="0" t="s">
         <v>155</v>
       </c>
@@ -9335,13 +9344,13 @@
         <v>144</v>
       </c>
       <c r="S151" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T151" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="152">
+      <c r="A152" s="0">
+        <v>151</v>
+      </c>
       <c r="B152" s="0" t="s">
         <v>156</v>
       </c>
@@ -9355,7 +9364,7 @@
         <v>59</v>
       </c>
       <c r="F152" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G152" s="0">
         <v>110</v>
@@ -9392,13 +9401,13 @@
         <v>144</v>
       </c>
       <c r="S152" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T152" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="153">
+      <c r="A153" s="0">
+        <v>152</v>
+      </c>
       <c r="B153" s="0" t="s">
         <v>19</v>
       </c>
@@ -9449,15 +9458,15 @@
         <v>144</v>
       </c>
       <c r="S153" s="0" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="0">
+        <v>153</v>
+      </c>
+      <c r="B154" s="0" t="s">
         <v>26</v>
-      </c>
-      <c r="T153" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="B154" s="0" t="s">
-        <v>27</v>
       </c>
       <c r="C154" s="0" t="s">
         <v>142</v>
@@ -9469,7 +9478,7 @@
         <v>21</v>
       </c>
       <c r="F154" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G154" s="0">
         <v>110</v>
@@ -9506,13 +9515,13 @@
         <v>144</v>
       </c>
       <c r="S154" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T154" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="155">
+      <c r="A155" s="0">
+        <v>154</v>
+      </c>
       <c r="B155" s="0" t="s">
         <v>159</v>
       </c>
@@ -9563,13 +9572,13 @@
         <v>161</v>
       </c>
       <c r="S155" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T155" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="156">
+      <c r="A156" s="0">
+        <v>155</v>
+      </c>
       <c r="B156" s="0" t="s">
         <v>162</v>
       </c>
@@ -9583,7 +9592,7 @@
         <v>21</v>
       </c>
       <c r="F156" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G156" s="0">
         <v>60</v>
@@ -9620,13 +9629,13 @@
         <v>161</v>
       </c>
       <c r="S156" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T156" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="157">
+      <c r="A157" s="0">
+        <v>156</v>
+      </c>
       <c r="B157" s="0" t="s">
         <v>163</v>
       </c>
@@ -9677,13 +9686,13 @@
         <v>161</v>
       </c>
       <c r="S157" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T157" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="158">
+      <c r="A158" s="0">
+        <v>157</v>
+      </c>
       <c r="B158" s="0" t="s">
         <v>164</v>
       </c>
@@ -9734,13 +9743,13 @@
         <v>161</v>
       </c>
       <c r="S158" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T158" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="159">
+      <c r="A159" s="0">
+        <v>158</v>
+      </c>
       <c r="B159" s="0" t="s">
         <v>165</v>
       </c>
@@ -9791,13 +9800,13 @@
         <v>161</v>
       </c>
       <c r="S159" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T159" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="160">
+      <c r="A160" s="0">
+        <v>159</v>
+      </c>
       <c r="B160" s="0" t="s">
         <v>166</v>
       </c>
@@ -9848,13 +9857,13 @@
         <v>161</v>
       </c>
       <c r="S160" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T160" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="161">
+      <c r="A161" s="0">
+        <v>160</v>
+      </c>
       <c r="B161" s="0" t="s">
         <v>167</v>
       </c>
@@ -9905,13 +9914,13 @@
         <v>161</v>
       </c>
       <c r="S161" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T161" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="162">
+      <c r="A162" s="0">
+        <v>161</v>
+      </c>
       <c r="B162" s="0" t="s">
         <v>168</v>
       </c>
@@ -9962,13 +9971,13 @@
         <v>161</v>
       </c>
       <c r="S162" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T162" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="163">
+      <c r="A163" s="0">
+        <v>162</v>
+      </c>
       <c r="B163" s="0" t="s">
         <v>141</v>
       </c>
@@ -10019,13 +10028,13 @@
         <v>161</v>
       </c>
       <c r="S163" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T163" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="164">
+      <c r="A164" s="0">
+        <v>163</v>
+      </c>
       <c r="B164" s="0" t="s">
         <v>145</v>
       </c>
@@ -10076,13 +10085,13 @@
         <v>161</v>
       </c>
       <c r="S164" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T164" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="165">
+      <c r="A165" s="0">
+        <v>164</v>
+      </c>
       <c r="B165" s="0" t="s">
         <v>146</v>
       </c>
@@ -10133,13 +10142,13 @@
         <v>161</v>
       </c>
       <c r="S165" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T165" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="166">
+      <c r="A166" s="0">
+        <v>165</v>
+      </c>
       <c r="B166" s="0" t="s">
         <v>147</v>
       </c>
@@ -10190,13 +10199,13 @@
         <v>161</v>
       </c>
       <c r="S166" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T166" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="167">
+      <c r="A167" s="0">
+        <v>166</v>
+      </c>
       <c r="B167" s="0" t="s">
         <v>148</v>
       </c>
@@ -10247,13 +10256,13 @@
         <v>161</v>
       </c>
       <c r="S167" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T167" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="168">
+      <c r="A168" s="0">
+        <v>167</v>
+      </c>
       <c r="B168" s="0" t="s">
         <v>151</v>
       </c>
@@ -10304,13 +10313,13 @@
         <v>161</v>
       </c>
       <c r="S168" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T168" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="169">
+      <c r="A169" s="0">
+        <v>168</v>
+      </c>
       <c r="B169" s="0" t="s">
         <v>153</v>
       </c>
@@ -10361,13 +10370,13 @@
         <v>161</v>
       </c>
       <c r="S169" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T169" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="170">
+      <c r="A170" s="0">
+        <v>169</v>
+      </c>
       <c r="B170" s="0" t="s">
         <v>154</v>
       </c>
@@ -10418,13 +10427,13 @@
         <v>161</v>
       </c>
       <c r="S170" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T170" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="171">
+      <c r="A171" s="0">
+        <v>170</v>
+      </c>
       <c r="B171" s="0" t="s">
         <v>175</v>
       </c>
@@ -10475,13 +10484,13 @@
         <v>161</v>
       </c>
       <c r="S171" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T171" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="172">
+      <c r="A172" s="0">
+        <v>171</v>
+      </c>
       <c r="B172" s="0" t="s">
         <v>176</v>
       </c>
@@ -10495,7 +10504,7 @@
         <v>59</v>
       </c>
       <c r="F172" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G172" s="0">
         <v>70</v>
@@ -10532,13 +10541,13 @@
         <v>161</v>
       </c>
       <c r="S172" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T172" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="173">
+      <c r="A173" s="0">
+        <v>172</v>
+      </c>
       <c r="B173" s="0" t="s">
         <v>177</v>
       </c>
@@ -10589,13 +10598,13 @@
         <v>161</v>
       </c>
       <c r="S173" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T173" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="174">
+      <c r="A174" s="0">
+        <v>173</v>
+      </c>
       <c r="B174" s="0" t="s">
         <v>178</v>
       </c>
@@ -10646,13 +10655,13 @@
         <v>161</v>
       </c>
       <c r="S174" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T174" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="175">
+      <c r="A175" s="0">
+        <v>174</v>
+      </c>
       <c r="B175" s="0" t="s">
         <v>19</v>
       </c>
@@ -10703,15 +10712,15 @@
         <v>161</v>
       </c>
       <c r="S175" s="0" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="0">
+        <v>175</v>
+      </c>
+      <c r="B176" s="0" t="s">
         <v>26</v>
-      </c>
-      <c r="T175" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="B176" s="0" t="s">
-        <v>27</v>
       </c>
       <c r="C176" s="0" t="s">
         <v>160</v>
@@ -10723,7 +10732,7 @@
         <v>21</v>
       </c>
       <c r="F176" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G176" s="0">
         <v>330</v>
@@ -10760,13 +10769,13 @@
         <v>161</v>
       </c>
       <c r="S176" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T176" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="177">
+      <c r="A177" s="0">
+        <v>176</v>
+      </c>
       <c r="B177" s="0" t="s">
         <v>181</v>
       </c>
@@ -10817,13 +10826,13 @@
         <v>161</v>
       </c>
       <c r="S177" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T177" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="178">
+      <c r="A178" s="0">
+        <v>177</v>
+      </c>
       <c r="B178" s="0" t="s">
         <v>182</v>
       </c>
@@ -10837,7 +10846,7 @@
         <v>59</v>
       </c>
       <c r="F178" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G178" s="0">
         <v>40</v>
@@ -10874,13 +10883,13 @@
         <v>161</v>
       </c>
       <c r="S178" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T178" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="179">
+      <c r="A179" s="0">
+        <v>178</v>
+      </c>
       <c r="B179" s="0" t="s">
         <v>183</v>
       </c>
@@ -10931,13 +10940,13 @@
         <v>161</v>
       </c>
       <c r="S179" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T179" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="180">
+      <c r="A180" s="0">
+        <v>179</v>
+      </c>
       <c r="B180" s="0" t="s">
         <v>184</v>
       </c>
@@ -10988,13 +10997,13 @@
         <v>161</v>
       </c>
       <c r="S180" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T180" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="181">
+      <c r="A181" s="0">
+        <v>180</v>
+      </c>
       <c r="B181" s="0" t="s">
         <v>185</v>
       </c>
@@ -11045,13 +11054,13 @@
         <v>161</v>
       </c>
       <c r="S181" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T181" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="182">
+      <c r="A182" s="0">
+        <v>181</v>
+      </c>
       <c r="B182" s="0" t="s">
         <v>186</v>
       </c>
@@ -11065,7 +11074,7 @@
         <v>59</v>
       </c>
       <c r="F182" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G182" s="0">
         <v>50</v>
@@ -11102,13 +11111,13 @@
         <v>161</v>
       </c>
       <c r="S182" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T182" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="183">
+      <c r="A183" s="0">
+        <v>182</v>
+      </c>
       <c r="B183" s="0" t="s">
         <v>30</v>
       </c>
@@ -11159,13 +11168,13 @@
         <v>161</v>
       </c>
       <c r="S183" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T183" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="184">
+      <c r="A184" s="0">
+        <v>183</v>
+      </c>
       <c r="B184" s="0" t="s">
         <v>32</v>
       </c>
@@ -11179,7 +11188,7 @@
         <v>21</v>
       </c>
       <c r="F184" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G184" s="0">
         <v>10</v>
@@ -11216,13 +11225,13 @@
         <v>161</v>
       </c>
       <c r="S184" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T184" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="185">
+      <c r="A185" s="0">
+        <v>184</v>
+      </c>
       <c r="B185" s="0" t="s">
         <v>33</v>
       </c>
@@ -11273,13 +11282,13 @@
         <v>161</v>
       </c>
       <c r="S185" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T185" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="186">
+      <c r="A186" s="0">
+        <v>185</v>
+      </c>
       <c r="B186" s="0" t="s">
         <v>35</v>
       </c>
@@ -11293,7 +11302,7 @@
         <v>21</v>
       </c>
       <c r="F186" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G186" s="0">
         <v>20</v>
@@ -11330,13 +11339,13 @@
         <v>161</v>
       </c>
       <c r="S186" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T186" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="187">
+      <c r="A187" s="0">
+        <v>186</v>
+      </c>
       <c r="B187" s="0" t="s">
         <v>36</v>
       </c>
@@ -11387,13 +11396,13 @@
         <v>161</v>
       </c>
       <c r="S187" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T187" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="188">
+      <c r="A188" s="0">
+        <v>187</v>
+      </c>
       <c r="B188" s="0" t="s">
         <v>38</v>
       </c>
@@ -11407,7 +11416,7 @@
         <v>21</v>
       </c>
       <c r="F188" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G188" s="0">
         <v>40</v>
@@ -11444,13 +11453,13 @@
         <v>161</v>
       </c>
       <c r="S188" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T188" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="189">
+      <c r="A189" s="0">
+        <v>188</v>
+      </c>
       <c r="B189" s="0" t="s">
         <v>39</v>
       </c>
@@ -11501,13 +11510,13 @@
         <v>161</v>
       </c>
       <c r="S189" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T189" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="190">
+      <c r="A190" s="0">
+        <v>189</v>
+      </c>
       <c r="B190" s="0" t="s">
         <v>41</v>
       </c>
@@ -11521,7 +11530,7 @@
         <v>21</v>
       </c>
       <c r="F190" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G190" s="0">
         <v>40</v>
@@ -11558,13 +11567,13 @@
         <v>161</v>
       </c>
       <c r="S190" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T190" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="191">
+      <c r="A191" s="0">
+        <v>190</v>
+      </c>
       <c r="B191" s="0" t="s">
         <v>42</v>
       </c>
@@ -11615,13 +11624,13 @@
         <v>161</v>
       </c>
       <c r="S191" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T191" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="192">
+      <c r="A192" s="0">
+        <v>191</v>
+      </c>
       <c r="B192" s="0" t="s">
         <v>44</v>
       </c>
@@ -11635,7 +11644,7 @@
         <v>21</v>
       </c>
       <c r="F192" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G192" s="0">
         <v>10</v>
@@ -11672,13 +11681,13 @@
         <v>161</v>
       </c>
       <c r="S192" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T192" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="193">
+      <c r="A193" s="0">
+        <v>192</v>
+      </c>
       <c r="B193" s="0" t="s">
         <v>45</v>
       </c>
@@ -11729,13 +11738,13 @@
         <v>161</v>
       </c>
       <c r="S193" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T193" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="194">
+      <c r="A194" s="0">
+        <v>193</v>
+      </c>
       <c r="B194" s="0" t="s">
         <v>47</v>
       </c>
@@ -11749,7 +11758,7 @@
         <v>21</v>
       </c>
       <c r="F194" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G194" s="0">
         <v>40</v>
@@ -11786,13 +11795,13 @@
         <v>161</v>
       </c>
       <c r="S194" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T194" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="195">
+      <c r="A195" s="0">
+        <v>194</v>
+      </c>
       <c r="B195" s="0" t="s">
         <v>51</v>
       </c>
@@ -11843,13 +11852,13 @@
         <v>161</v>
       </c>
       <c r="S195" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T195" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="196">
+      <c r="A196" s="0">
+        <v>195</v>
+      </c>
       <c r="B196" s="0" t="s">
         <v>53</v>
       </c>
@@ -11863,7 +11872,7 @@
         <v>21</v>
       </c>
       <c r="F196" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G196" s="0">
         <v>40</v>
@@ -11900,13 +11909,13 @@
         <v>161</v>
       </c>
       <c r="S196" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T196" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="197">
+      <c r="A197" s="0">
+        <v>196</v>
+      </c>
       <c r="B197" s="0" t="s">
         <v>54</v>
       </c>
@@ -11957,13 +11966,13 @@
         <v>161</v>
       </c>
       <c r="S197" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T197" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="198">
+      <c r="A198" s="0">
+        <v>197</v>
+      </c>
       <c r="B198" s="0" t="s">
         <v>56</v>
       </c>
@@ -11977,7 +11986,7 @@
         <v>21</v>
       </c>
       <c r="F198" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G198" s="0">
         <v>10</v>
@@ -12014,13 +12023,13 @@
         <v>161</v>
       </c>
       <c r="S198" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T198" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="199">
+      <c r="A199" s="0">
+        <v>198</v>
+      </c>
       <c r="B199" s="0" t="s">
         <v>58</v>
       </c>
@@ -12071,13 +12080,13 @@
         <v>161</v>
       </c>
       <c r="S199" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T199" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="200">
+      <c r="A200" s="0">
+        <v>199</v>
+      </c>
       <c r="B200" s="0" t="s">
         <v>60</v>
       </c>
@@ -12091,7 +12100,7 @@
         <v>59</v>
       </c>
       <c r="F200" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G200" s="0">
         <v>10</v>
@@ -12128,13 +12137,13 @@
         <v>161</v>
       </c>
       <c r="S200" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T200" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="201">
+      <c r="A201" s="0">
+        <v>200</v>
+      </c>
       <c r="B201" s="0" t="s">
         <v>61</v>
       </c>
@@ -12185,13 +12194,13 @@
         <v>161</v>
       </c>
       <c r="S201" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T201" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="202">
+      <c r="A202" s="0">
+        <v>201</v>
+      </c>
       <c r="B202" s="0" t="s">
         <v>63</v>
       </c>
@@ -12205,7 +12214,7 @@
         <v>59</v>
       </c>
       <c r="F202" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G202" s="0">
         <v>10</v>
@@ -12242,13 +12251,13 @@
         <v>161</v>
       </c>
       <c r="S202" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T202" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="203">
+      <c r="A203" s="0">
+        <v>202</v>
+      </c>
       <c r="B203" s="0" t="s">
         <v>191</v>
       </c>
@@ -12299,13 +12308,13 @@
         <v>161</v>
       </c>
       <c r="S203" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T203" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="204">
+      <c r="A204" s="0">
+        <v>203</v>
+      </c>
       <c r="B204" s="0" t="s">
         <v>192</v>
       </c>
@@ -12319,7 +12328,7 @@
         <v>59</v>
       </c>
       <c r="F204" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G204" s="0">
         <v>10</v>
@@ -12356,13 +12365,13 @@
         <v>161</v>
       </c>
       <c r="S204" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T204" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="205">
+      <c r="A205" s="0">
+        <v>204</v>
+      </c>
       <c r="B205" s="0" t="s">
         <v>64</v>
       </c>
@@ -12413,13 +12422,13 @@
         <v>161</v>
       </c>
       <c r="S205" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T205" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="206">
+      <c r="A206" s="0">
+        <v>205</v>
+      </c>
       <c r="B206" s="0" t="s">
         <v>66</v>
       </c>
@@ -12433,7 +12442,7 @@
         <v>21</v>
       </c>
       <c r="F206" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G206" s="0">
         <v>70</v>
@@ -12470,13 +12479,13 @@
         <v>161</v>
       </c>
       <c r="S206" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T206" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="207">
+      <c r="A207" s="0">
+        <v>206</v>
+      </c>
       <c r="B207" s="0" t="s">
         <v>68</v>
       </c>
@@ -12527,13 +12536,13 @@
         <v>161</v>
       </c>
       <c r="S207" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T207" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="208">
+      <c r="A208" s="0">
+        <v>207</v>
+      </c>
       <c r="B208" s="0" t="s">
         <v>75</v>
       </c>
@@ -12584,13 +12593,13 @@
         <v>196</v>
       </c>
       <c r="S208" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T208" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="209">
+      <c r="A209" s="0">
+        <v>208</v>
+      </c>
       <c r="B209" s="0" t="s">
         <v>77</v>
       </c>
@@ -12604,7 +12613,7 @@
         <v>59</v>
       </c>
       <c r="F209" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G209" s="0">
         <v>60</v>
@@ -12641,13 +12650,13 @@
         <v>196</v>
       </c>
       <c r="S209" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T209" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="210">
+      <c r="A210" s="0">
+        <v>209</v>
+      </c>
       <c r="B210" s="0" t="s">
         <v>78</v>
       </c>
@@ -12698,13 +12707,13 @@
         <v>196</v>
       </c>
       <c r="S210" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T210" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="211">
+      <c r="A211" s="0">
+        <v>210</v>
+      </c>
       <c r="B211" s="0" t="s">
         <v>79</v>
       </c>
@@ -12755,13 +12764,13 @@
         <v>196</v>
       </c>
       <c r="S211" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T211" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="212">
+      <c r="A212" s="0">
+        <v>211</v>
+      </c>
       <c r="B212" s="0" t="s">
         <v>81</v>
       </c>
@@ -12812,13 +12821,13 @@
         <v>196</v>
       </c>
       <c r="S212" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T212" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="213">
+      <c r="A213" s="0">
+        <v>212</v>
+      </c>
       <c r="B213" s="0" t="s">
         <v>70</v>
       </c>
@@ -12869,13 +12878,13 @@
         <v>197</v>
       </c>
       <c r="S213" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T213" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="214">
+      <c r="A214" s="0">
+        <v>213</v>
+      </c>
       <c r="B214" s="0" t="s">
         <v>198</v>
       </c>
@@ -12889,7 +12898,7 @@
         <v>59</v>
       </c>
       <c r="F214" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G214" s="0">
         <v>10</v>
@@ -12926,13 +12935,13 @@
         <v>197</v>
       </c>
       <c r="S214" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T214" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="215">
+      <c r="A215" s="0">
+        <v>214</v>
+      </c>
       <c r="B215" s="0" t="s">
         <v>199</v>
       </c>
@@ -12983,13 +12992,13 @@
         <v>197</v>
       </c>
       <c r="S215" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T215" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="216">
+      <c r="A216" s="0">
+        <v>215</v>
+      </c>
       <c r="B216" s="0" t="s">
         <v>200</v>
       </c>
@@ -13040,13 +13049,13 @@
         <v>197</v>
       </c>
       <c r="S216" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T216" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="217">
+      <c r="A217" s="0">
+        <v>216</v>
+      </c>
       <c r="B217" s="0" t="s">
         <v>201</v>
       </c>
@@ -13097,13 +13106,13 @@
         <v>197</v>
       </c>
       <c r="S217" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T217" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="218">
+      <c r="A218" s="0">
+        <v>217</v>
+      </c>
       <c r="B218" s="0" t="s">
         <v>202</v>
       </c>
@@ -13154,13 +13163,13 @@
         <v>197</v>
       </c>
       <c r="S218" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T218" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="219">
+      <c r="A219" s="0">
+        <v>218</v>
+      </c>
       <c r="B219" s="0" t="s">
         <v>203</v>
       </c>
@@ -13174,7 +13183,7 @@
         <v>59</v>
       </c>
       <c r="F219" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G219" s="0">
         <v>40</v>
@@ -13211,13 +13220,13 @@
         <v>197</v>
       </c>
       <c r="S219" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T219" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="220">
+      <c r="A220" s="0">
+        <v>219</v>
+      </c>
       <c r="B220" s="0" t="s">
         <v>111</v>
       </c>
@@ -13268,13 +13277,13 @@
         <v>197</v>
       </c>
       <c r="S220" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T220" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="221">
+      <c r="A221" s="0">
+        <v>220</v>
+      </c>
       <c r="B221" s="0" t="s">
         <v>112</v>
       </c>
@@ -13288,7 +13297,7 @@
         <v>21</v>
       </c>
       <c r="F221" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G221" s="0">
         <v>60</v>
@@ -13325,13 +13334,13 @@
         <v>197</v>
       </c>
       <c r="S221" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T221" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="222">
+      <c r="A222" s="0">
+        <v>221</v>
+      </c>
       <c r="B222" s="0" t="s">
         <v>113</v>
       </c>
@@ -13382,13 +13391,13 @@
         <v>197</v>
       </c>
       <c r="S222" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T222" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="223">
+      <c r="A223" s="0">
+        <v>222</v>
+      </c>
       <c r="B223" s="0" t="s">
         <v>159</v>
       </c>
@@ -13439,13 +13448,13 @@
         <v>205</v>
       </c>
       <c r="S223" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T223" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="224">
+      <c r="A224" s="0">
+        <v>223</v>
+      </c>
       <c r="B224" s="0" t="s">
         <v>162</v>
       </c>
@@ -13459,7 +13468,7 @@
         <v>21</v>
       </c>
       <c r="F224" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G224" s="0">
         <v>30</v>
@@ -13496,13 +13505,13 @@
         <v>205</v>
       </c>
       <c r="S224" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T224" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="225">
+      <c r="A225" s="0">
+        <v>224</v>
+      </c>
       <c r="B225" s="0" t="s">
         <v>163</v>
       </c>
@@ -13553,13 +13562,13 @@
         <v>205</v>
       </c>
       <c r="S225" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T225" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="226">
+      <c r="A226" s="0">
+        <v>225</v>
+      </c>
       <c r="B226" s="0" t="s">
         <v>164</v>
       </c>
@@ -13610,13 +13619,13 @@
         <v>205</v>
       </c>
       <c r="S226" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T226" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="227">
+      <c r="A227" s="0">
+        <v>226</v>
+      </c>
       <c r="B227" s="0" t="s">
         <v>165</v>
       </c>
@@ -13667,13 +13676,13 @@
         <v>205</v>
       </c>
       <c r="S227" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T227" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="228">
+      <c r="A228" s="0">
+        <v>227</v>
+      </c>
       <c r="B228" s="0" t="s">
         <v>166</v>
       </c>
@@ -13724,13 +13733,13 @@
         <v>205</v>
       </c>
       <c r="S228" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T228" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="229">
+      <c r="A229" s="0">
+        <v>228</v>
+      </c>
       <c r="B229" s="0" t="s">
         <v>167</v>
       </c>
@@ -13781,13 +13790,13 @@
         <v>205</v>
       </c>
       <c r="S229" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T229" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="230">
+      <c r="A230" s="0">
+        <v>229</v>
+      </c>
       <c r="B230" s="0" t="s">
         <v>168</v>
       </c>
@@ -13838,13 +13847,13 @@
         <v>205</v>
       </c>
       <c r="S230" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T230" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="231">
+      <c r="A231" s="0">
+        <v>230</v>
+      </c>
       <c r="B231" s="0" t="s">
         <v>141</v>
       </c>
@@ -13895,13 +13904,13 @@
         <v>205</v>
       </c>
       <c r="S231" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T231" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="232">
+      <c r="A232" s="0">
+        <v>231</v>
+      </c>
       <c r="B232" s="0" t="s">
         <v>145</v>
       </c>
@@ -13952,13 +13961,13 @@
         <v>205</v>
       </c>
       <c r="S232" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T232" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="233">
+      <c r="A233" s="0">
+        <v>232</v>
+      </c>
       <c r="B233" s="0" t="s">
         <v>146</v>
       </c>
@@ -14009,13 +14018,13 @@
         <v>205</v>
       </c>
       <c r="S233" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T233" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="234">
+      <c r="A234" s="0">
+        <v>233</v>
+      </c>
       <c r="B234" s="0" t="s">
         <v>147</v>
       </c>
@@ -14066,13 +14075,13 @@
         <v>205</v>
       </c>
       <c r="S234" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T234" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="235">
+      <c r="A235" s="0">
+        <v>234</v>
+      </c>
       <c r="B235" s="0" t="s">
         <v>148</v>
       </c>
@@ -14123,13 +14132,13 @@
         <v>205</v>
       </c>
       <c r="S235" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T235" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="236">
+      <c r="A236" s="0">
+        <v>235</v>
+      </c>
       <c r="B236" s="0" t="s">
         <v>149</v>
       </c>
@@ -14180,13 +14189,13 @@
         <v>205</v>
       </c>
       <c r="S236" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T236" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="237">
+      <c r="A237" s="0">
+        <v>236</v>
+      </c>
       <c r="B237" s="0" t="s">
         <v>151</v>
       </c>
@@ -14237,13 +14246,13 @@
         <v>205</v>
       </c>
       <c r="S237" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T237" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="238">
+      <c r="A238" s="0">
+        <v>237</v>
+      </c>
       <c r="B238" s="0" t="s">
         <v>153</v>
       </c>
@@ -14294,13 +14303,13 @@
         <v>205</v>
       </c>
       <c r="S238" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T238" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="239">
+      <c r="A239" s="0">
+        <v>238</v>
+      </c>
       <c r="B239" s="0" t="s">
         <v>154</v>
       </c>
@@ -14351,13 +14360,13 @@
         <v>205</v>
       </c>
       <c r="S239" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T239" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="240">
+      <c r="A240" s="0">
+        <v>239</v>
+      </c>
       <c r="B240" s="0" t="s">
         <v>155</v>
       </c>
@@ -14408,13 +14417,13 @@
         <v>205</v>
       </c>
       <c r="S240" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T240" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="241">
+      <c r="A241" s="0">
+        <v>240</v>
+      </c>
       <c r="B241" s="0" t="s">
         <v>156</v>
       </c>
@@ -14428,7 +14437,7 @@
         <v>59</v>
       </c>
       <c r="F241" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G241" s="0">
         <v>30</v>
@@ -14465,13 +14474,13 @@
         <v>205</v>
       </c>
       <c r="S241" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T241" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="242">
+      <c r="A242" s="0">
+        <v>241</v>
+      </c>
       <c r="B242" s="0" t="s">
         <v>175</v>
       </c>
@@ -14522,13 +14531,13 @@
         <v>205</v>
       </c>
       <c r="S242" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T242" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="243">
+      <c r="A243" s="0">
+        <v>242</v>
+      </c>
       <c r="B243" s="0" t="s">
         <v>176</v>
       </c>
@@ -14542,7 +14551,7 @@
         <v>59</v>
       </c>
       <c r="F243" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G243" s="0">
         <v>30</v>
@@ -14579,13 +14588,13 @@
         <v>205</v>
       </c>
       <c r="S243" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T243" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="244">
+      <c r="A244" s="0">
+        <v>243</v>
+      </c>
       <c r="B244" s="0" t="s">
         <v>177</v>
       </c>
@@ -14636,13 +14645,13 @@
         <v>205</v>
       </c>
       <c r="S244" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T244" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="245">
+      <c r="A245" s="0">
+        <v>244</v>
+      </c>
       <c r="B245" s="0" t="s">
         <v>178</v>
       </c>
@@ -14693,13 +14702,13 @@
         <v>205</v>
       </c>
       <c r="S245" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T245" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="246">
+      <c r="A246" s="0">
+        <v>245</v>
+      </c>
       <c r="B246" s="0" t="s">
         <v>19</v>
       </c>
@@ -14750,15 +14759,15 @@
         <v>205</v>
       </c>
       <c r="S246" s="0" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="0">
+        <v>246</v>
+      </c>
+      <c r="B247" s="0" t="s">
         <v>26</v>
-      </c>
-      <c r="T246" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="B247" s="0" t="s">
-        <v>27</v>
       </c>
       <c r="C247" s="0" t="s">
         <v>204</v>
@@ -14770,7 +14779,7 @@
         <v>21</v>
       </c>
       <c r="F247" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G247" s="0">
         <v>30</v>
@@ -14807,13 +14816,13 @@
         <v>205</v>
       </c>
       <c r="S247" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T247" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="248">
+      <c r="A248" s="0">
+        <v>247</v>
+      </c>
       <c r="B248" s="0" t="s">
         <v>181</v>
       </c>
@@ -14864,13 +14873,13 @@
         <v>205</v>
       </c>
       <c r="S248" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T248" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="249">
+      <c r="A249" s="0">
+        <v>248</v>
+      </c>
       <c r="B249" s="0" t="s">
         <v>182</v>
       </c>
@@ -14884,7 +14893,7 @@
         <v>59</v>
       </c>
       <c r="F249" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G249" s="0">
         <v>30</v>
@@ -14921,13 +14930,13 @@
         <v>205</v>
       </c>
       <c r="S249" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T249" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="250">
+      <c r="A250" s="0">
+        <v>249</v>
+      </c>
       <c r="B250" s="0" t="s">
         <v>183</v>
       </c>
@@ -14978,13 +14987,13 @@
         <v>205</v>
       </c>
       <c r="S250" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T250" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="251">
+      <c r="A251" s="0">
+        <v>250</v>
+      </c>
       <c r="B251" s="0" t="s">
         <v>184</v>
       </c>
@@ -15035,13 +15044,13 @@
         <v>205</v>
       </c>
       <c r="S251" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T251" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="252">
+      <c r="A252" s="0">
+        <v>251</v>
+      </c>
       <c r="B252" s="0" t="s">
         <v>185</v>
       </c>
@@ -15092,13 +15101,13 @@
         <v>205</v>
       </c>
       <c r="S252" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T252" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="253">
+      <c r="A253" s="0">
+        <v>252</v>
+      </c>
       <c r="B253" s="0" t="s">
         <v>186</v>
       </c>
@@ -15112,7 +15121,7 @@
         <v>59</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G253" s="0">
         <v>30</v>
@@ -15149,13 +15158,13 @@
         <v>205</v>
       </c>
       <c r="S253" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T253" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="254">
+      <c r="A254" s="0">
+        <v>253</v>
+      </c>
       <c r="B254" s="0" t="s">
         <v>30</v>
       </c>
@@ -15206,13 +15215,13 @@
         <v>205</v>
       </c>
       <c r="S254" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T254" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="255">
+      <c r="A255" s="0">
+        <v>254</v>
+      </c>
       <c r="B255" s="0" t="s">
         <v>32</v>
       </c>
@@ -15226,7 +15235,7 @@
         <v>21</v>
       </c>
       <c r="F255" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G255" s="0">
         <v>30</v>
@@ -15263,13 +15272,13 @@
         <v>205</v>
       </c>
       <c r="S255" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T255" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="256">
+      <c r="A256" s="0">
+        <v>255</v>
+      </c>
       <c r="B256" s="0" t="s">
         <v>33</v>
       </c>
@@ -15320,13 +15329,13 @@
         <v>205</v>
       </c>
       <c r="S256" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T256" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="257">
+      <c r="A257" s="0">
+        <v>256</v>
+      </c>
       <c r="B257" s="0" t="s">
         <v>35</v>
       </c>
@@ -15340,7 +15349,7 @@
         <v>21</v>
       </c>
       <c r="F257" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G257" s="0">
         <v>30</v>
@@ -15377,13 +15386,13 @@
         <v>205</v>
       </c>
       <c r="S257" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T257" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="258">
+      <c r="A258" s="0">
+        <v>257</v>
+      </c>
       <c r="B258" s="0" t="s">
         <v>36</v>
       </c>
@@ -15434,13 +15443,13 @@
         <v>205</v>
       </c>
       <c r="S258" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T258" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="259">
+      <c r="A259" s="0">
+        <v>258</v>
+      </c>
       <c r="B259" s="0" t="s">
         <v>38</v>
       </c>
@@ -15454,7 +15463,7 @@
         <v>21</v>
       </c>
       <c r="F259" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G259" s="0">
         <v>30</v>
@@ -15491,13 +15500,13 @@
         <v>205</v>
       </c>
       <c r="S259" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T259" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="260">
+      <c r="A260" s="0">
+        <v>259</v>
+      </c>
       <c r="B260" s="0" t="s">
         <v>39</v>
       </c>
@@ -15548,13 +15557,13 @@
         <v>205</v>
       </c>
       <c r="S260" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T260" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="261">
+      <c r="A261" s="0">
+        <v>260</v>
+      </c>
       <c r="B261" s="0" t="s">
         <v>41</v>
       </c>
@@ -15568,7 +15577,7 @@
         <v>21</v>
       </c>
       <c r="F261" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G261" s="0">
         <v>30</v>
@@ -15605,13 +15614,13 @@
         <v>205</v>
       </c>
       <c r="S261" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T261" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="262">
+      <c r="A262" s="0">
+        <v>261</v>
+      </c>
       <c r="B262" s="0" t="s">
         <v>42</v>
       </c>
@@ -15662,13 +15671,13 @@
         <v>205</v>
       </c>
       <c r="S262" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T262" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="263">
+      <c r="A263" s="0">
+        <v>262</v>
+      </c>
       <c r="B263" s="0" t="s">
         <v>44</v>
       </c>
@@ -15682,7 +15691,7 @@
         <v>21</v>
       </c>
       <c r="F263" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G263" s="0">
         <v>30</v>
@@ -15719,13 +15728,13 @@
         <v>205</v>
       </c>
       <c r="S263" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T263" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="264">
+      <c r="A264" s="0">
+        <v>263</v>
+      </c>
       <c r="B264" s="0" t="s">
         <v>45</v>
       </c>
@@ -15776,13 +15785,13 @@
         <v>205</v>
       </c>
       <c r="S264" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T264" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="265">
+      <c r="A265" s="0">
+        <v>264</v>
+      </c>
       <c r="B265" s="0" t="s">
         <v>47</v>
       </c>
@@ -15796,7 +15805,7 @@
         <v>21</v>
       </c>
       <c r="F265" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G265" s="0">
         <v>30</v>
@@ -15833,13 +15842,13 @@
         <v>205</v>
       </c>
       <c r="S265" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T265" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="266">
+      <c r="A266" s="0">
+        <v>265</v>
+      </c>
       <c r="B266" s="0" t="s">
         <v>48</v>
       </c>
@@ -15890,13 +15899,13 @@
         <v>205</v>
       </c>
       <c r="S266" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T266" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="267">
+      <c r="A267" s="0">
+        <v>266</v>
+      </c>
       <c r="B267" s="0" t="s">
         <v>50</v>
       </c>
@@ -15910,7 +15919,7 @@
         <v>21</v>
       </c>
       <c r="F267" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G267" s="0">
         <v>30</v>
@@ -15947,13 +15956,13 @@
         <v>205</v>
       </c>
       <c r="S267" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T267" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="268">
+      <c r="A268" s="0">
+        <v>267</v>
+      </c>
       <c r="B268" s="0" t="s">
         <v>51</v>
       </c>
@@ -16004,13 +16013,13 @@
         <v>205</v>
       </c>
       <c r="S268" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T268" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="269">
+      <c r="A269" s="0">
+        <v>268</v>
+      </c>
       <c r="B269" s="0" t="s">
         <v>53</v>
       </c>
@@ -16024,7 +16033,7 @@
         <v>21</v>
       </c>
       <c r="F269" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G269" s="0">
         <v>30</v>
@@ -16061,13 +16070,13 @@
         <v>205</v>
       </c>
       <c r="S269" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T269" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="270">
+      <c r="A270" s="0">
+        <v>269</v>
+      </c>
       <c r="B270" s="0" t="s">
         <v>54</v>
       </c>
@@ -16118,13 +16127,13 @@
         <v>205</v>
       </c>
       <c r="S270" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T270" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="271">
+      <c r="A271" s="0">
+        <v>270</v>
+      </c>
       <c r="B271" s="0" t="s">
         <v>56</v>
       </c>
@@ -16138,7 +16147,7 @@
         <v>21</v>
       </c>
       <c r="F271" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G271" s="0">
         <v>30</v>
@@ -16175,13 +16184,13 @@
         <v>205</v>
       </c>
       <c r="S271" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T271" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="272">
+      <c r="A272" s="0">
+        <v>271</v>
+      </c>
       <c r="B272" s="0" t="s">
         <v>58</v>
       </c>
@@ -16232,13 +16241,13 @@
         <v>205</v>
       </c>
       <c r="S272" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T272" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="273">
+      <c r="A273" s="0">
+        <v>272</v>
+      </c>
       <c r="B273" s="0" t="s">
         <v>60</v>
       </c>
@@ -16252,7 +16261,7 @@
         <v>59</v>
       </c>
       <c r="F273" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G273" s="0">
         <v>30</v>
@@ -16289,13 +16298,13 @@
         <v>205</v>
       </c>
       <c r="S273" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T273" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="274">
+      <c r="A274" s="0">
+        <v>273</v>
+      </c>
       <c r="B274" s="0" t="s">
         <v>61</v>
       </c>
@@ -16346,13 +16355,13 @@
         <v>205</v>
       </c>
       <c r="S274" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T274" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="275">
+      <c r="A275" s="0">
+        <v>274</v>
+      </c>
       <c r="B275" s="0" t="s">
         <v>63</v>
       </c>
@@ -16366,7 +16375,7 @@
         <v>59</v>
       </c>
       <c r="F275" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G275" s="0">
         <v>30</v>
@@ -16403,13 +16412,13 @@
         <v>205</v>
       </c>
       <c r="S275" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T275" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="276">
+      <c r="A276" s="0">
+        <v>275</v>
+      </c>
       <c r="B276" s="0" t="s">
         <v>102</v>
       </c>
@@ -16460,13 +16469,13 @@
         <v>205</v>
       </c>
       <c r="S276" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T276" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="277">
+      <c r="A277" s="0">
+        <v>276</v>
+      </c>
       <c r="B277" s="0" t="s">
         <v>191</v>
       </c>
@@ -16517,13 +16526,13 @@
         <v>205</v>
       </c>
       <c r="S277" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T277" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="278">
+      <c r="A278" s="0">
+        <v>277</v>
+      </c>
       <c r="B278" s="0" t="s">
         <v>192</v>
       </c>
@@ -16537,7 +16546,7 @@
         <v>59</v>
       </c>
       <c r="F278" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G278" s="0">
         <v>30</v>
@@ -16574,13 +16583,13 @@
         <v>205</v>
       </c>
       <c r="S278" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T278" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="279">
+      <c r="A279" s="0">
+        <v>278</v>
+      </c>
       <c r="B279" s="0" t="s">
         <v>64</v>
       </c>
@@ -16631,13 +16640,13 @@
         <v>205</v>
       </c>
       <c r="S279" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T279" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="280">
+      <c r="A280" s="0">
+        <v>279</v>
+      </c>
       <c r="B280" s="0" t="s">
         <v>66</v>
       </c>
@@ -16651,7 +16660,7 @@
         <v>21</v>
       </c>
       <c r="F280" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G280" s="0">
         <v>30</v>
@@ -16688,13 +16697,13 @@
         <v>205</v>
       </c>
       <c r="S280" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T280" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="281">
+      <c r="A281" s="0">
+        <v>280</v>
+      </c>
       <c r="B281" s="0" t="s">
         <v>68</v>
       </c>
@@ -16745,13 +16754,13 @@
         <v>205</v>
       </c>
       <c r="S281" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T281" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="282">
+      <c r="A282" s="0">
+        <v>281</v>
+      </c>
       <c r="B282" s="0" t="s">
         <v>75</v>
       </c>
@@ -16802,13 +16811,13 @@
         <v>205</v>
       </c>
       <c r="S282" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T282" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="283">
+      <c r="A283" s="0">
+        <v>282</v>
+      </c>
       <c r="B283" s="0" t="s">
         <v>77</v>
       </c>
@@ -16822,7 +16831,7 @@
         <v>59</v>
       </c>
       <c r="F283" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G283" s="0">
         <v>30</v>
@@ -16859,13 +16868,13 @@
         <v>205</v>
       </c>
       <c r="S283" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T283" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="284">
+      <c r="A284" s="0">
+        <v>283</v>
+      </c>
       <c r="B284" s="0" t="s">
         <v>78</v>
       </c>
@@ -16916,13 +16925,13 @@
         <v>205</v>
       </c>
       <c r="S284" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T284" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="285">
+      <c r="A285" s="0">
+        <v>284</v>
+      </c>
       <c r="B285" s="0" t="s">
         <v>79</v>
       </c>
@@ -16973,13 +16982,13 @@
         <v>205</v>
       </c>
       <c r="S285" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T285" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="286">
+      <c r="A286" s="0">
+        <v>285</v>
+      </c>
       <c r="B286" s="0" t="s">
         <v>81</v>
       </c>
@@ -17030,13 +17039,13 @@
         <v>205</v>
       </c>
       <c r="S286" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T286" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="287">
+      <c r="A287" s="0">
+        <v>286</v>
+      </c>
       <c r="B287" s="0" t="s">
         <v>70</v>
       </c>
@@ -17087,13 +17096,13 @@
         <v>205</v>
       </c>
       <c r="S287" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T287" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="288">
+      <c r="A288" s="0">
+        <v>287</v>
+      </c>
       <c r="B288" s="0" t="s">
         <v>198</v>
       </c>
@@ -17107,7 +17116,7 @@
         <v>59</v>
       </c>
       <c r="F288" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G288" s="0">
         <v>30</v>
@@ -17144,13 +17153,13 @@
         <v>205</v>
       </c>
       <c r="S288" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T288" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="289">
+      <c r="A289" s="0">
+        <v>288</v>
+      </c>
       <c r="B289" s="0" t="s">
         <v>199</v>
       </c>
@@ -17201,13 +17210,13 @@
         <v>205</v>
       </c>
       <c r="S289" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T289" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="290">
+      <c r="A290" s="0">
+        <v>289</v>
+      </c>
       <c r="B290" s="0" t="s">
         <v>200</v>
       </c>
@@ -17258,13 +17267,13 @@
         <v>205</v>
       </c>
       <c r="S290" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T290" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="291">
+      <c r="A291" s="0">
+        <v>290</v>
+      </c>
       <c r="B291" s="0" t="s">
         <v>201</v>
       </c>
@@ -17315,13 +17324,13 @@
         <v>205</v>
       </c>
       <c r="S291" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T291" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="292">
+      <c r="A292" s="0">
+        <v>291</v>
+      </c>
       <c r="B292" s="0" t="s">
         <v>202</v>
       </c>
@@ -17372,13 +17381,13 @@
         <v>205</v>
       </c>
       <c r="S292" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T292" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="293">
+      <c r="A293" s="0">
+        <v>292</v>
+      </c>
       <c r="B293" s="0" t="s">
         <v>203</v>
       </c>
@@ -17392,7 +17401,7 @@
         <v>59</v>
       </c>
       <c r="F293" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G293" s="0">
         <v>30</v>
@@ -17429,13 +17438,13 @@
         <v>205</v>
       </c>
       <c r="S293" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T293" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="294">
+      <c r="A294" s="0">
+        <v>293</v>
+      </c>
       <c r="B294" s="0" t="s">
         <v>111</v>
       </c>
@@ -17486,13 +17495,13 @@
         <v>205</v>
       </c>
       <c r="S294" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T294" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="295">
+      <c r="A295" s="0">
+        <v>294</v>
+      </c>
       <c r="B295" s="0" t="s">
         <v>112</v>
       </c>
@@ -17506,7 +17515,7 @@
         <v>21</v>
       </c>
       <c r="F295" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G295" s="0">
         <v>30</v>
@@ -17543,13 +17552,13 @@
         <v>205</v>
       </c>
       <c r="S295" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T295" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="296">
+      <c r="A296" s="0">
+        <v>295</v>
+      </c>
       <c r="B296" s="0" t="s">
         <v>113</v>
       </c>
@@ -17600,10 +17609,7 @@
         <v>205</v>
       </c>
       <c r="S296" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T296" s="0">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/wwwroot/92/BoxBreakingReport.xlsx
+++ b/wwwroot/92/BoxBreakingReport.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="204">
   <si>
     <t>SerialNo</t>
   </si>
@@ -624,45 +624,6 @@
   </si>
   <si>
     <t>MPED104(A)</t>
-  </si>
-  <si>
-    <t>University Extra</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>3 to 5</t>
-  </si>
-  <si>
-    <t>40 to 42</t>
-  </si>
-  <si>
-    <t>35 to 37</t>
-  </si>
-  <si>
-    <t>2 to 4</t>
-  </si>
-  <si>
-    <t>17 to 19</t>
-  </si>
-  <si>
-    <t>41 to 43</t>
-  </si>
-  <si>
-    <t>31 to 33</t>
-  </si>
-  <si>
-    <t>15 to 17</t>
-  </si>
-  <si>
-    <t>18 to 20</t>
-  </si>
-  <si>
-    <t>16 to 18</t>
-  </si>
-  <si>
-    <t>14 to 16</t>
   </si>
 </sst>
 </file>
@@ -714,12 +675,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
-  <dimension ref="A1:S296"/>
+  <dimension ref="A1:S222"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
     <col min="2" max="2" width="16.057085037231445" customWidth="1"/>
-    <col min="3" max="3" width="16.09404182434082" customWidth="1"/>
+    <col min="3" max="3" width="12.745315551757812" customWidth="1"/>
     <col min="4" max="4" width="11.811811447143555" customWidth="1"/>
     <col min="5" max="5" width="22.885726928710938" customWidth="1"/>
     <col min="6" max="6" width="13.382554054260254" customWidth="1"/>
@@ -13394,4224 +13355,6 @@
         <v>29</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="0">
-        <v>222</v>
-      </c>
-      <c r="B223" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="C223" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D223" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E223" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F223" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G223" s="0">
-        <v>30</v>
-      </c>
-      <c r="H223"/>
-      <c r="I223" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J223" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K223" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L223" s="0">
-        <v>3</v>
-      </c>
-      <c r="M223" s="0">
-        <v>4</v>
-      </c>
-      <c r="N223" s="0">
-        <v>6</v>
-      </c>
-      <c r="O223" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="P223" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q223" s="0">
-        <v>120</v>
-      </c>
-      <c r="R223" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S223" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="0">
-        <v>223</v>
-      </c>
-      <c r="B224" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="C224" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D224" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E224" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F224" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G224" s="0">
-        <v>30</v>
-      </c>
-      <c r="H224"/>
-      <c r="I224" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J224" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K224" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L224" s="0">
-        <v>3</v>
-      </c>
-      <c r="M224" s="0">
-        <v>3</v>
-      </c>
-      <c r="N224" s="0">
-        <v>5</v>
-      </c>
-      <c r="O224" s="0" t="s">
-        <v>206</v>
-      </c>
-      <c r="P224" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q224" s="0">
-        <v>120</v>
-      </c>
-      <c r="R224" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S224" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="0">
-        <v>224</v>
-      </c>
-      <c r="B225" s="0" t="s">
-        <v>163</v>
-      </c>
-      <c r="C225" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D225" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E225" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F225" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="G225" s="0">
-        <v>30</v>
-      </c>
-      <c r="H225"/>
-      <c r="I225" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J225" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K225" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L225" s="0">
-        <v>3</v>
-      </c>
-      <c r="M225" s="0">
-        <v>4</v>
-      </c>
-      <c r="N225" s="0">
-        <v>6</v>
-      </c>
-      <c r="O225" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="P225" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q225" s="0">
-        <v>120</v>
-      </c>
-      <c r="R225" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S225" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="0">
-        <v>225</v>
-      </c>
-      <c r="B226" s="0" t="s">
-        <v>164</v>
-      </c>
-      <c r="C226" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D226" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E226" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F226" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="G226" s="0">
-        <v>30</v>
-      </c>
-      <c r="H226"/>
-      <c r="I226" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J226" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K226" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L226" s="0">
-        <v>3</v>
-      </c>
-      <c r="M226" s="0">
-        <v>3</v>
-      </c>
-      <c r="N226" s="0">
-        <v>5</v>
-      </c>
-      <c r="O226" s="0" t="s">
-        <v>206</v>
-      </c>
-      <c r="P226" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q226" s="0">
-        <v>120</v>
-      </c>
-      <c r="R226" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S226" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="0">
-        <v>226</v>
-      </c>
-      <c r="B227" s="0" t="s">
-        <v>165</v>
-      </c>
-      <c r="C227" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D227" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E227" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F227" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="G227" s="0">
-        <v>30</v>
-      </c>
-      <c r="H227"/>
-      <c r="I227" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J227" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K227" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L227" s="0">
-        <v>3</v>
-      </c>
-      <c r="M227" s="0">
-        <v>4</v>
-      </c>
-      <c r="N227" s="0">
-        <v>6</v>
-      </c>
-      <c r="O227" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="P227" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q227" s="0">
-        <v>120</v>
-      </c>
-      <c r="R227" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S227" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="0">
-        <v>227</v>
-      </c>
-      <c r="B228" s="0" t="s">
-        <v>166</v>
-      </c>
-      <c r="C228" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D228" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E228" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F228" s="0" t="s">
-        <v>152</v>
-      </c>
-      <c r="G228" s="0">
-        <v>30</v>
-      </c>
-      <c r="H228"/>
-      <c r="I228" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J228" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K228" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L228" s="0">
-        <v>3</v>
-      </c>
-      <c r="M228" s="0">
-        <v>3</v>
-      </c>
-      <c r="N228" s="0">
-        <v>5</v>
-      </c>
-      <c r="O228" s="0" t="s">
-        <v>206</v>
-      </c>
-      <c r="P228" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q228" s="0">
-        <v>120</v>
-      </c>
-      <c r="R228" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S228" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="0">
-        <v>228</v>
-      </c>
-      <c r="B229" s="0" t="s">
-        <v>167</v>
-      </c>
-      <c r="C229" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D229" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E229" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F229" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="G229" s="0">
-        <v>30</v>
-      </c>
-      <c r="H229"/>
-      <c r="I229" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J229" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K229" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L229" s="0">
-        <v>3</v>
-      </c>
-      <c r="M229" s="0">
-        <v>3</v>
-      </c>
-      <c r="N229" s="0">
-        <v>5</v>
-      </c>
-      <c r="O229" s="0" t="s">
-        <v>206</v>
-      </c>
-      <c r="P229" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q229" s="0">
-        <v>120</v>
-      </c>
-      <c r="R229" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S229" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="0">
-        <v>229</v>
-      </c>
-      <c r="B230" s="0" t="s">
-        <v>168</v>
-      </c>
-      <c r="C230" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D230" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E230" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F230" s="0" t="s">
-        <v>169</v>
-      </c>
-      <c r="G230" s="0">
-        <v>30</v>
-      </c>
-      <c r="H230"/>
-      <c r="I230" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J230" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K230" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L230" s="0">
-        <v>3</v>
-      </c>
-      <c r="M230" s="0">
-        <v>3</v>
-      </c>
-      <c r="N230" s="0">
-        <v>5</v>
-      </c>
-      <c r="O230" s="0" t="s">
-        <v>206</v>
-      </c>
-      <c r="P230" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q230" s="0">
-        <v>120</v>
-      </c>
-      <c r="R230" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S230" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="0">
-        <v>230</v>
-      </c>
-      <c r="B231" s="0" t="s">
-        <v>141</v>
-      </c>
-      <c r="C231" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D231" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E231" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F231" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="G231" s="0">
-        <v>30</v>
-      </c>
-      <c r="H231"/>
-      <c r="I231" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J231" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K231" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L231" s="0">
-        <v>3</v>
-      </c>
-      <c r="M231" s="0">
-        <v>5</v>
-      </c>
-      <c r="N231" s="0">
-        <v>7</v>
-      </c>
-      <c r="O231" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="P231" s="0">
-        <v>7</v>
-      </c>
-      <c r="Q231" s="0">
-        <v>210</v>
-      </c>
-      <c r="R231" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S231" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="0">
-        <v>231</v>
-      </c>
-      <c r="B232" s="0" t="s">
-        <v>145</v>
-      </c>
-      <c r="C232" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D232" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E232" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F232" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="G232" s="0">
-        <v>30</v>
-      </c>
-      <c r="H232"/>
-      <c r="I232" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J232" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K232" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L232" s="0">
-        <v>3</v>
-      </c>
-      <c r="M232" s="0">
-        <v>7</v>
-      </c>
-      <c r="N232" s="0">
-        <v>9</v>
-      </c>
-      <c r="O232" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="P232" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q232" s="0">
-        <v>120</v>
-      </c>
-      <c r="R232" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S232" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="0">
-        <v>232</v>
-      </c>
-      <c r="B233" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="C233" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D233" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E233" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F233" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="G233" s="0">
-        <v>30</v>
-      </c>
-      <c r="H233"/>
-      <c r="I233" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J233" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K233" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L233" s="0">
-        <v>3</v>
-      </c>
-      <c r="M233" s="0">
-        <v>3</v>
-      </c>
-      <c r="N233" s="0">
-        <v>5</v>
-      </c>
-      <c r="O233" s="0" t="s">
-        <v>206</v>
-      </c>
-      <c r="P233" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q233" s="0">
-        <v>120</v>
-      </c>
-      <c r="R233" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S233" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="0">
-        <v>233</v>
-      </c>
-      <c r="B234" s="0" t="s">
-        <v>147</v>
-      </c>
-      <c r="C234" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D234" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E234" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F234" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="G234" s="0">
-        <v>30</v>
-      </c>
-      <c r="H234"/>
-      <c r="I234" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J234" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K234" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L234" s="0">
-        <v>3</v>
-      </c>
-      <c r="M234" s="0">
-        <v>7</v>
-      </c>
-      <c r="N234" s="0">
-        <v>9</v>
-      </c>
-      <c r="O234" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="P234" s="0">
-        <v>8</v>
-      </c>
-      <c r="Q234" s="0">
-        <v>240</v>
-      </c>
-      <c r="R234" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S234" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="0">
-        <v>234</v>
-      </c>
-      <c r="B235" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="C235" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D235" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E235" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F235" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="G235" s="0">
-        <v>30</v>
-      </c>
-      <c r="H235"/>
-      <c r="I235" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J235" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K235" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L235" s="0">
-        <v>3</v>
-      </c>
-      <c r="M235" s="0">
-        <v>4</v>
-      </c>
-      <c r="N235" s="0">
-        <v>6</v>
-      </c>
-      <c r="O235" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="P235" s="0">
-        <v>8</v>
-      </c>
-      <c r="Q235" s="0">
-        <v>240</v>
-      </c>
-      <c r="R235" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S235" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="0">
-        <v>235</v>
-      </c>
-      <c r="B236" s="0" t="s">
-        <v>149</v>
-      </c>
-      <c r="C236" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D236" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E236" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F236" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="G236" s="0">
-        <v>30</v>
-      </c>
-      <c r="H236"/>
-      <c r="I236" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J236" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K236" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L236" s="0">
-        <v>3</v>
-      </c>
-      <c r="M236" s="0">
-        <v>5</v>
-      </c>
-      <c r="N236" s="0">
-        <v>7</v>
-      </c>
-      <c r="O236" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="P236" s="0">
-        <v>8</v>
-      </c>
-      <c r="Q236" s="0">
-        <v>240</v>
-      </c>
-      <c r="R236" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S236" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="0">
-        <v>236</v>
-      </c>
-      <c r="B237" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="C237" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D237" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E237" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F237" s="0" t="s">
-        <v>152</v>
-      </c>
-      <c r="G237" s="0">
-        <v>30</v>
-      </c>
-      <c r="H237"/>
-      <c r="I237" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J237" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K237" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L237" s="0">
-        <v>3</v>
-      </c>
-      <c r="M237" s="0">
-        <v>4</v>
-      </c>
-      <c r="N237" s="0">
-        <v>6</v>
-      </c>
-      <c r="O237" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="P237" s="0">
-        <v>8</v>
-      </c>
-      <c r="Q237" s="0">
-        <v>240</v>
-      </c>
-      <c r="R237" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S237" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="0">
-        <v>237</v>
-      </c>
-      <c r="B238" s="0" t="s">
-        <v>153</v>
-      </c>
-      <c r="C238" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D238" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E238" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F238" s="0" t="s">
-        <v>152</v>
-      </c>
-      <c r="G238" s="0">
-        <v>30</v>
-      </c>
-      <c r="H238"/>
-      <c r="I238" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J238" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K238" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L238" s="0">
-        <v>3</v>
-      </c>
-      <c r="M238" s="0">
-        <v>3</v>
-      </c>
-      <c r="N238" s="0">
-        <v>5</v>
-      </c>
-      <c r="O238" s="0" t="s">
-        <v>206</v>
-      </c>
-      <c r="P238" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q238" s="0">
-        <v>120</v>
-      </c>
-      <c r="R238" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S238" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="0">
-        <v>238</v>
-      </c>
-      <c r="B239" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="C239" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D239" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E239" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F239" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="G239" s="0">
-        <v>30</v>
-      </c>
-      <c r="H239"/>
-      <c r="I239" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J239" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K239" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L239" s="0">
-        <v>3</v>
-      </c>
-      <c r="M239" s="0">
-        <v>5</v>
-      </c>
-      <c r="N239" s="0">
-        <v>7</v>
-      </c>
-      <c r="O239" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="P239" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q239" s="0">
-        <v>120</v>
-      </c>
-      <c r="R239" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S239" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="0">
-        <v>239</v>
-      </c>
-      <c r="B240" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="C240" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D240" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E240" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F240" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G240" s="0">
-        <v>30</v>
-      </c>
-      <c r="H240"/>
-      <c r="I240" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J240" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K240" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L240" s="0">
-        <v>3</v>
-      </c>
-      <c r="M240" s="0">
-        <v>4</v>
-      </c>
-      <c r="N240" s="0">
-        <v>6</v>
-      </c>
-      <c r="O240" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="P240" s="0">
-        <v>8</v>
-      </c>
-      <c r="Q240" s="0">
-        <v>240</v>
-      </c>
-      <c r="R240" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S240" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="0">
-        <v>240</v>
-      </c>
-      <c r="B241" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="C241" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D241" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E241" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F241" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G241" s="0">
-        <v>30</v>
-      </c>
-      <c r="H241"/>
-      <c r="I241" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J241" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K241" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L241" s="0">
-        <v>3</v>
-      </c>
-      <c r="M241" s="0">
-        <v>3</v>
-      </c>
-      <c r="N241" s="0">
-        <v>5</v>
-      </c>
-      <c r="O241" s="0" t="s">
-        <v>206</v>
-      </c>
-      <c r="P241" s="0">
-        <v>7</v>
-      </c>
-      <c r="Q241" s="0">
-        <v>210</v>
-      </c>
-      <c r="R241" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S241" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="0">
-        <v>241</v>
-      </c>
-      <c r="B242" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="C242" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D242" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E242" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F242" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G242" s="0">
-        <v>30</v>
-      </c>
-      <c r="H242"/>
-      <c r="I242" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J242" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K242" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L242" s="0">
-        <v>3</v>
-      </c>
-      <c r="M242" s="0">
-        <v>4</v>
-      </c>
-      <c r="N242" s="0">
-        <v>6</v>
-      </c>
-      <c r="O242" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="P242" s="0">
-        <v>3</v>
-      </c>
-      <c r="Q242" s="0">
-        <v>90</v>
-      </c>
-      <c r="R242" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S242" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="0">
-        <v>242</v>
-      </c>
-      <c r="B243" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="C243" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D243" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E243" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F243" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G243" s="0">
-        <v>30</v>
-      </c>
-      <c r="H243"/>
-      <c r="I243" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J243" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K243" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L243" s="0">
-        <v>3</v>
-      </c>
-      <c r="M243" s="0">
-        <v>4</v>
-      </c>
-      <c r="N243" s="0">
-        <v>6</v>
-      </c>
-      <c r="O243" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="P243" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q243" s="0">
-        <v>120</v>
-      </c>
-      <c r="R243" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S243" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="0">
-        <v>243</v>
-      </c>
-      <c r="B244" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="C244" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D244" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E244" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F244" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="G244" s="0">
-        <v>30</v>
-      </c>
-      <c r="H244"/>
-      <c r="I244" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J244" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K244" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L244" s="0">
-        <v>3</v>
-      </c>
-      <c r="M244" s="0">
-        <v>4</v>
-      </c>
-      <c r="N244" s="0">
-        <v>6</v>
-      </c>
-      <c r="O244" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="P244" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q244" s="0">
-        <v>120</v>
-      </c>
-      <c r="R244" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S244" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="0">
-        <v>244</v>
-      </c>
-      <c r="B245" s="0" t="s">
-        <v>178</v>
-      </c>
-      <c r="C245" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D245" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E245" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F245" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="G245" s="0">
-        <v>30</v>
-      </c>
-      <c r="H245"/>
-      <c r="I245" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J245" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K245" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L245" s="0">
-        <v>3</v>
-      </c>
-      <c r="M245" s="0">
-        <v>4</v>
-      </c>
-      <c r="N245" s="0">
-        <v>6</v>
-      </c>
-      <c r="O245" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="P245" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q245" s="0">
-        <v>120</v>
-      </c>
-      <c r="R245" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S245" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="0">
-        <v>245</v>
-      </c>
-      <c r="B246" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="C246" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D246" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E246" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F246" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G246" s="0">
-        <v>30</v>
-      </c>
-      <c r="H246"/>
-      <c r="I246" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J246" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K246" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L246" s="0">
-        <v>3</v>
-      </c>
-      <c r="M246" s="0">
-        <v>40</v>
-      </c>
-      <c r="N246" s="0">
-        <v>42</v>
-      </c>
-      <c r="O246" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="P246" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q246" s="0">
-        <v>120</v>
-      </c>
-      <c r="R246" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S246" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="0">
-        <v>246</v>
-      </c>
-      <c r="B247" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C247" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D247" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E247" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F247" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G247" s="0">
-        <v>30</v>
-      </c>
-      <c r="H247"/>
-      <c r="I247" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J247" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K247" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L247" s="0">
-        <v>3</v>
-      </c>
-      <c r="M247" s="0">
-        <v>35</v>
-      </c>
-      <c r="N247" s="0">
-        <v>37</v>
-      </c>
-      <c r="O247" s="0" t="s">
-        <v>208</v>
-      </c>
-      <c r="P247" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q247" s="0">
-        <v>120</v>
-      </c>
-      <c r="R247" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S247" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="0">
-        <v>247</v>
-      </c>
-      <c r="B248" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="C248" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D248" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E248" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F248" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G248" s="0">
-        <v>30</v>
-      </c>
-      <c r="H248"/>
-      <c r="I248" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J248" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K248" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L248" s="0">
-        <v>3</v>
-      </c>
-      <c r="M248" s="0">
-        <v>5</v>
-      </c>
-      <c r="N248" s="0">
-        <v>7</v>
-      </c>
-      <c r="O248" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="P248" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q248" s="0">
-        <v>120</v>
-      </c>
-      <c r="R248" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S248" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="0">
-        <v>248</v>
-      </c>
-      <c r="B249" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="C249" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D249" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E249" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F249" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G249" s="0">
-        <v>30</v>
-      </c>
-      <c r="H249"/>
-      <c r="I249" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J249" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K249" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L249" s="0">
-        <v>3</v>
-      </c>
-      <c r="M249" s="0">
-        <v>5</v>
-      </c>
-      <c r="N249" s="0">
-        <v>7</v>
-      </c>
-      <c r="O249" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="P249" s="0">
-        <v>7</v>
-      </c>
-      <c r="Q249" s="0">
-        <v>210</v>
-      </c>
-      <c r="R249" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S249" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="0">
-        <v>249</v>
-      </c>
-      <c r="B250" s="0" t="s">
-        <v>183</v>
-      </c>
-      <c r="C250" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D250" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E250" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F250" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="G250" s="0">
-        <v>30</v>
-      </c>
-      <c r="H250"/>
-      <c r="I250" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J250" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K250" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L250" s="0">
-        <v>3</v>
-      </c>
-      <c r="M250" s="0">
-        <v>5</v>
-      </c>
-      <c r="N250" s="0">
-        <v>7</v>
-      </c>
-      <c r="O250" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="P250" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q250" s="0">
-        <v>120</v>
-      </c>
-      <c r="R250" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S250" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="0">
-        <v>250</v>
-      </c>
-      <c r="B251" s="0" t="s">
-        <v>184</v>
-      </c>
-      <c r="C251" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D251" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E251" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F251" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="G251" s="0">
-        <v>30</v>
-      </c>
-      <c r="H251"/>
-      <c r="I251" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J251" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K251" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L251" s="0">
-        <v>3</v>
-      </c>
-      <c r="M251" s="0">
-        <v>5</v>
-      </c>
-      <c r="N251" s="0">
-        <v>7</v>
-      </c>
-      <c r="O251" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="P251" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q251" s="0">
-        <v>120</v>
-      </c>
-      <c r="R251" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S251" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="0">
-        <v>251</v>
-      </c>
-      <c r="B252" s="0" t="s">
-        <v>185</v>
-      </c>
-      <c r="C252" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D252" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E252" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F252" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G252" s="0">
-        <v>30</v>
-      </c>
-      <c r="H252"/>
-      <c r="I252" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J252" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K252" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L252" s="0">
-        <v>3</v>
-      </c>
-      <c r="M252" s="0">
-        <v>2</v>
-      </c>
-      <c r="N252" s="0">
-        <v>4</v>
-      </c>
-      <c r="O252" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="P252" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q252" s="0">
-        <v>120</v>
-      </c>
-      <c r="R252" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S252" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="0">
-        <v>252</v>
-      </c>
-      <c r="B253" s="0" t="s">
-        <v>186</v>
-      </c>
-      <c r="C253" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D253" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E253" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F253" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G253" s="0">
-        <v>30</v>
-      </c>
-      <c r="H253"/>
-      <c r="I253" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J253" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K253" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L253" s="0">
-        <v>3</v>
-      </c>
-      <c r="M253" s="0">
-        <v>2</v>
-      </c>
-      <c r="N253" s="0">
-        <v>4</v>
-      </c>
-      <c r="O253" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="P253" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q253" s="0">
-        <v>120</v>
-      </c>
-      <c r="R253" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S253" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="0">
-        <v>253</v>
-      </c>
-      <c r="B254" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="C254" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D254" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E254" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F254" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G254" s="0">
-        <v>30</v>
-      </c>
-      <c r="H254"/>
-      <c r="I254" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J254" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K254" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L254" s="0">
-        <v>3</v>
-      </c>
-      <c r="M254" s="0">
-        <v>17</v>
-      </c>
-      <c r="N254" s="0">
-        <v>19</v>
-      </c>
-      <c r="O254" s="0" t="s">
-        <v>210</v>
-      </c>
-      <c r="P254" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q254" s="0">
-        <v>120</v>
-      </c>
-      <c r="R254" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S254" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="0">
-        <v>254</v>
-      </c>
-      <c r="B255" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C255" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D255" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E255" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F255" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G255" s="0">
-        <v>30</v>
-      </c>
-      <c r="H255"/>
-      <c r="I255" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J255" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K255" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L255" s="0">
-        <v>3</v>
-      </c>
-      <c r="M255" s="0">
-        <v>17</v>
-      </c>
-      <c r="N255" s="0">
-        <v>19</v>
-      </c>
-      <c r="O255" s="0" t="s">
-        <v>210</v>
-      </c>
-      <c r="P255" s="0">
-        <v>7</v>
-      </c>
-      <c r="Q255" s="0">
-        <v>210</v>
-      </c>
-      <c r="R255" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S255" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="0">
-        <v>255</v>
-      </c>
-      <c r="B256" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C256" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D256" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E256" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F256" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G256" s="0">
-        <v>30</v>
-      </c>
-      <c r="H256"/>
-      <c r="I256" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J256" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K256" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L256" s="0">
-        <v>3</v>
-      </c>
-      <c r="M256" s="0">
-        <v>23</v>
-      </c>
-      <c r="N256" s="0">
-        <v>25</v>
-      </c>
-      <c r="O256" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="P256" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q256" s="0">
-        <v>120</v>
-      </c>
-      <c r="R256" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S256" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="0">
-        <v>256</v>
-      </c>
-      <c r="B257" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="C257" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D257" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E257" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F257" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G257" s="0">
-        <v>30</v>
-      </c>
-      <c r="H257"/>
-      <c r="I257" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J257" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K257" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L257" s="0">
-        <v>3</v>
-      </c>
-      <c r="M257" s="0">
-        <v>23</v>
-      </c>
-      <c r="N257" s="0">
-        <v>25</v>
-      </c>
-      <c r="O257" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="P257" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q257" s="0">
-        <v>120</v>
-      </c>
-      <c r="R257" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S257" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="0">
-        <v>257</v>
-      </c>
-      <c r="B258" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="C258" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D258" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E258" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F258" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G258" s="0">
-        <v>30</v>
-      </c>
-      <c r="H258"/>
-      <c r="I258" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J258" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K258" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L258" s="0">
-        <v>3</v>
-      </c>
-      <c r="M258" s="0">
-        <v>41</v>
-      </c>
-      <c r="N258" s="0">
-        <v>43</v>
-      </c>
-      <c r="O258" s="0" t="s">
-        <v>211</v>
-      </c>
-      <c r="P258" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q258" s="0">
-        <v>120</v>
-      </c>
-      <c r="R258" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S258" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="0">
-        <v>258</v>
-      </c>
-      <c r="B259" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C259" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D259" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E259" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F259" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G259" s="0">
-        <v>30</v>
-      </c>
-      <c r="H259"/>
-      <c r="I259" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J259" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K259" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L259" s="0">
-        <v>3</v>
-      </c>
-      <c r="M259" s="0">
-        <v>41</v>
-      </c>
-      <c r="N259" s="0">
-        <v>43</v>
-      </c>
-      <c r="O259" s="0" t="s">
-        <v>211</v>
-      </c>
-      <c r="P259" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q259" s="0">
-        <v>120</v>
-      </c>
-      <c r="R259" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S259" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="0">
-        <v>259</v>
-      </c>
-      <c r="B260" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="C260" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D260" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E260" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F260" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G260" s="0">
-        <v>30</v>
-      </c>
-      <c r="H260"/>
-      <c r="I260" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J260" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K260" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L260" s="0">
-        <v>3</v>
-      </c>
-      <c r="M260" s="0">
-        <v>23</v>
-      </c>
-      <c r="N260" s="0">
-        <v>25</v>
-      </c>
-      <c r="O260" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="P260" s="0">
-        <v>8</v>
-      </c>
-      <c r="Q260" s="0">
-        <v>240</v>
-      </c>
-      <c r="R260" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S260" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="0">
-        <v>260</v>
-      </c>
-      <c r="B261" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="C261" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D261" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E261" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F261" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G261" s="0">
-        <v>30</v>
-      </c>
-      <c r="H261"/>
-      <c r="I261" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J261" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K261" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L261" s="0">
-        <v>3</v>
-      </c>
-      <c r="M261" s="0">
-        <v>23</v>
-      </c>
-      <c r="N261" s="0">
-        <v>25</v>
-      </c>
-      <c r="O261" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="P261" s="0">
-        <v>7</v>
-      </c>
-      <c r="Q261" s="0">
-        <v>210</v>
-      </c>
-      <c r="R261" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S261" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="0">
-        <v>261</v>
-      </c>
-      <c r="B262" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="C262" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D262" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E262" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F262" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G262" s="0">
-        <v>30</v>
-      </c>
-      <c r="H262"/>
-      <c r="I262" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J262" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K262" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L262" s="0">
-        <v>3</v>
-      </c>
-      <c r="M262" s="0">
-        <v>4</v>
-      </c>
-      <c r="N262" s="0">
-        <v>6</v>
-      </c>
-      <c r="O262" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="P262" s="0">
-        <v>8</v>
-      </c>
-      <c r="Q262" s="0">
-        <v>240</v>
-      </c>
-      <c r="R262" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S262" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="0">
-        <v>262</v>
-      </c>
-      <c r="B263" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="C263" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D263" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E263" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F263" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G263" s="0">
-        <v>30</v>
-      </c>
-      <c r="H263"/>
-      <c r="I263" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J263" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K263" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L263" s="0">
-        <v>3</v>
-      </c>
-      <c r="M263" s="0">
-        <v>4</v>
-      </c>
-      <c r="N263" s="0">
-        <v>6</v>
-      </c>
-      <c r="O263" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="P263" s="0">
-        <v>8</v>
-      </c>
-      <c r="Q263" s="0">
-        <v>240</v>
-      </c>
-      <c r="R263" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S263" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="0">
-        <v>263</v>
-      </c>
-      <c r="B264" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="C264" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D264" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E264" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F264" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G264" s="0">
-        <v>30</v>
-      </c>
-      <c r="H264"/>
-      <c r="I264" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J264" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K264" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L264" s="0">
-        <v>3</v>
-      </c>
-      <c r="M264" s="0">
-        <v>31</v>
-      </c>
-      <c r="N264" s="0">
-        <v>33</v>
-      </c>
-      <c r="O264" s="0" t="s">
-        <v>212</v>
-      </c>
-      <c r="P264" s="0">
-        <v>7</v>
-      </c>
-      <c r="Q264" s="0">
-        <v>210</v>
-      </c>
-      <c r="R264" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S264" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="0">
-        <v>264</v>
-      </c>
-      <c r="B265" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C265" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D265" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E265" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F265" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G265" s="0">
-        <v>30</v>
-      </c>
-      <c r="H265"/>
-      <c r="I265" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J265" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K265" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L265" s="0">
-        <v>3</v>
-      </c>
-      <c r="M265" s="0">
-        <v>31</v>
-      </c>
-      <c r="N265" s="0">
-        <v>33</v>
-      </c>
-      <c r="O265" s="0" t="s">
-        <v>212</v>
-      </c>
-      <c r="P265" s="0">
-        <v>7</v>
-      </c>
-      <c r="Q265" s="0">
-        <v>210</v>
-      </c>
-      <c r="R265" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S265" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="0">
-        <v>265</v>
-      </c>
-      <c r="B266" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C266" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D266" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E266" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F266" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G266" s="0">
-        <v>30</v>
-      </c>
-      <c r="H266"/>
-      <c r="I266" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J266" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K266" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L266" s="0">
-        <v>3</v>
-      </c>
-      <c r="M266" s="0">
-        <v>2</v>
-      </c>
-      <c r="N266" s="0">
-        <v>4</v>
-      </c>
-      <c r="O266" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="P266" s="0">
-        <v>7</v>
-      </c>
-      <c r="Q266" s="0">
-        <v>210</v>
-      </c>
-      <c r="R266" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S266" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="0">
-        <v>266</v>
-      </c>
-      <c r="B267" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C267" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D267" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E267" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F267" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G267" s="0">
-        <v>30</v>
-      </c>
-      <c r="H267"/>
-      <c r="I267" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J267" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K267" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L267" s="0">
-        <v>3</v>
-      </c>
-      <c r="M267" s="0">
-        <v>2</v>
-      </c>
-      <c r="N267" s="0">
-        <v>4</v>
-      </c>
-      <c r="O267" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="P267" s="0">
-        <v>7</v>
-      </c>
-      <c r="Q267" s="0">
-        <v>210</v>
-      </c>
-      <c r="R267" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S267" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="0">
-        <v>267</v>
-      </c>
-      <c r="B268" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="C268" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D268" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E268" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F268" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G268" s="0">
-        <v>30</v>
-      </c>
-      <c r="H268"/>
-      <c r="I268" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J268" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K268" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L268" s="0">
-        <v>3</v>
-      </c>
-      <c r="M268" s="0">
-        <v>15</v>
-      </c>
-      <c r="N268" s="0">
-        <v>17</v>
-      </c>
-      <c r="O268" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="P268" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q268" s="0">
-        <v>120</v>
-      </c>
-      <c r="R268" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S268" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="0">
-        <v>268</v>
-      </c>
-      <c r="B269" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C269" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D269" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E269" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F269" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G269" s="0">
-        <v>30</v>
-      </c>
-      <c r="H269"/>
-      <c r="I269" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J269" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K269" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L269" s="0">
-        <v>3</v>
-      </c>
-      <c r="M269" s="0">
-        <v>15</v>
-      </c>
-      <c r="N269" s="0">
-        <v>17</v>
-      </c>
-      <c r="O269" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="P269" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q269" s="0">
-        <v>120</v>
-      </c>
-      <c r="R269" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S269" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="0">
-        <v>269</v>
-      </c>
-      <c r="B270" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C270" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D270" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E270" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F270" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G270" s="0">
-        <v>30</v>
-      </c>
-      <c r="H270"/>
-      <c r="I270" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J270" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K270" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L270" s="0">
-        <v>3</v>
-      </c>
-      <c r="M270" s="0">
-        <v>9</v>
-      </c>
-      <c r="N270" s="0">
-        <v>11</v>
-      </c>
-      <c r="O270" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="P270" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q270" s="0">
-        <v>120</v>
-      </c>
-      <c r="R270" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S270" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="0">
-        <v>270</v>
-      </c>
-      <c r="B271" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C271" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D271" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E271" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F271" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G271" s="0">
-        <v>30</v>
-      </c>
-      <c r="H271"/>
-      <c r="I271" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J271" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K271" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L271" s="0">
-        <v>3</v>
-      </c>
-      <c r="M271" s="0">
-        <v>9</v>
-      </c>
-      <c r="N271" s="0">
-        <v>11</v>
-      </c>
-      <c r="O271" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="P271" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q271" s="0">
-        <v>120</v>
-      </c>
-      <c r="R271" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S271" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="0">
-        <v>271</v>
-      </c>
-      <c r="B272" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="C272" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D272" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E272" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F272" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G272" s="0">
-        <v>30</v>
-      </c>
-      <c r="H272"/>
-      <c r="I272" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J272" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K272" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L272" s="0">
-        <v>3</v>
-      </c>
-      <c r="M272" s="0">
-        <v>18</v>
-      </c>
-      <c r="N272" s="0">
-        <v>20</v>
-      </c>
-      <c r="O272" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="P272" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q272" s="0">
-        <v>120</v>
-      </c>
-      <c r="R272" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S272" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="0">
-        <v>272</v>
-      </c>
-      <c r="B273" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="C273" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D273" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E273" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F273" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G273" s="0">
-        <v>30</v>
-      </c>
-      <c r="H273"/>
-      <c r="I273" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J273" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K273" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L273" s="0">
-        <v>3</v>
-      </c>
-      <c r="M273" s="0">
-        <v>18</v>
-      </c>
-      <c r="N273" s="0">
-        <v>20</v>
-      </c>
-      <c r="O273" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="P273" s="0">
-        <v>7</v>
-      </c>
-      <c r="Q273" s="0">
-        <v>210</v>
-      </c>
-      <c r="R273" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S273" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="0">
-        <v>273</v>
-      </c>
-      <c r="B274" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="C274" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D274" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E274" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F274" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G274" s="0">
-        <v>30</v>
-      </c>
-      <c r="H274"/>
-      <c r="I274" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J274" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K274" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L274" s="0">
-        <v>3</v>
-      </c>
-      <c r="M274" s="0">
-        <v>16</v>
-      </c>
-      <c r="N274" s="0">
-        <v>18</v>
-      </c>
-      <c r="O274" s="0" t="s">
-        <v>215</v>
-      </c>
-      <c r="P274" s="0">
-        <v>7</v>
-      </c>
-      <c r="Q274" s="0">
-        <v>210</v>
-      </c>
-      <c r="R274" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S274" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="0">
-        <v>274</v>
-      </c>
-      <c r="B275" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="C275" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D275" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E275" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F275" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G275" s="0">
-        <v>30</v>
-      </c>
-      <c r="H275"/>
-      <c r="I275" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J275" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K275" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L275" s="0">
-        <v>3</v>
-      </c>
-      <c r="M275" s="0">
-        <v>16</v>
-      </c>
-      <c r="N275" s="0">
-        <v>18</v>
-      </c>
-      <c r="O275" s="0" t="s">
-        <v>215</v>
-      </c>
-      <c r="P275" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q275" s="0">
-        <v>120</v>
-      </c>
-      <c r="R275" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S275" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="0">
-        <v>275</v>
-      </c>
-      <c r="B276" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="C276" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D276" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E276" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F276" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G276" s="0">
-        <v>30</v>
-      </c>
-      <c r="H276"/>
-      <c r="I276" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J276" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K276" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L276" s="0">
-        <v>3</v>
-      </c>
-      <c r="M276" s="0">
-        <v>5</v>
-      </c>
-      <c r="N276" s="0">
-        <v>7</v>
-      </c>
-      <c r="O276" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="P276" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q276" s="0">
-        <v>120</v>
-      </c>
-      <c r="R276" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S276" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="0">
-        <v>276</v>
-      </c>
-      <c r="B277" s="0" t="s">
-        <v>191</v>
-      </c>
-      <c r="C277" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D277" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E277" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F277" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G277" s="0">
-        <v>30</v>
-      </c>
-      <c r="H277"/>
-      <c r="I277" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J277" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K277" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L277" s="0">
-        <v>3</v>
-      </c>
-      <c r="M277" s="0">
-        <v>2</v>
-      </c>
-      <c r="N277" s="0">
-        <v>4</v>
-      </c>
-      <c r="O277" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="P277" s="0">
-        <v>7</v>
-      </c>
-      <c r="Q277" s="0">
-        <v>210</v>
-      </c>
-      <c r="R277" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S277" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="0">
-        <v>277</v>
-      </c>
-      <c r="B278" s="0" t="s">
-        <v>192</v>
-      </c>
-      <c r="C278" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D278" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E278" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F278" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G278" s="0">
-        <v>30</v>
-      </c>
-      <c r="H278"/>
-      <c r="I278" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J278" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K278" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L278" s="0">
-        <v>3</v>
-      </c>
-      <c r="M278" s="0">
-        <v>2</v>
-      </c>
-      <c r="N278" s="0">
-        <v>4</v>
-      </c>
-      <c r="O278" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="P278" s="0">
-        <v>7</v>
-      </c>
-      <c r="Q278" s="0">
-        <v>210</v>
-      </c>
-      <c r="R278" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S278" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="0">
-        <v>278</v>
-      </c>
-      <c r="B279" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="C279" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D279" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E279" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F279" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G279" s="0">
-        <v>30</v>
-      </c>
-      <c r="H279"/>
-      <c r="I279" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J279" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K279" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L279" s="0">
-        <v>3</v>
-      </c>
-      <c r="M279" s="0">
-        <v>15</v>
-      </c>
-      <c r="N279" s="0">
-        <v>17</v>
-      </c>
-      <c r="O279" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="P279" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q279" s="0">
-        <v>120</v>
-      </c>
-      <c r="R279" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S279" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="0">
-        <v>279</v>
-      </c>
-      <c r="B280" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="C280" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D280" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E280" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F280" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G280" s="0">
-        <v>30</v>
-      </c>
-      <c r="H280"/>
-      <c r="I280" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J280" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K280" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L280" s="0">
-        <v>3</v>
-      </c>
-      <c r="M280" s="0">
-        <v>14</v>
-      </c>
-      <c r="N280" s="0">
-        <v>16</v>
-      </c>
-      <c r="O280" s="0" t="s">
-        <v>216</v>
-      </c>
-      <c r="P280" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q280" s="0">
-        <v>120</v>
-      </c>
-      <c r="R280" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S280" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="0">
-        <v>280</v>
-      </c>
-      <c r="B281" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="C281" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D281" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E281" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F281" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="G281" s="0">
-        <v>30</v>
-      </c>
-      <c r="H281"/>
-      <c r="I281" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J281" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K281" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L281" s="0">
-        <v>3</v>
-      </c>
-      <c r="M281" s="0">
-        <v>15</v>
-      </c>
-      <c r="N281" s="0">
-        <v>17</v>
-      </c>
-      <c r="O281" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="P281" s="0">
-        <v>8</v>
-      </c>
-      <c r="Q281" s="0">
-        <v>240</v>
-      </c>
-      <c r="R281" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S281" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="0">
-        <v>281</v>
-      </c>
-      <c r="B282" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="C282" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D282" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E282" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F282" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G282" s="0">
-        <v>30</v>
-      </c>
-      <c r="H282"/>
-      <c r="I282" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J282" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K282" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L282" s="0">
-        <v>3</v>
-      </c>
-      <c r="M282" s="0">
-        <v>6</v>
-      </c>
-      <c r="N282" s="0">
-        <v>8</v>
-      </c>
-      <c r="O282" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="P282" s="0">
-        <v>7</v>
-      </c>
-      <c r="Q282" s="0">
-        <v>210</v>
-      </c>
-      <c r="R282" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S282" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="0">
-        <v>282</v>
-      </c>
-      <c r="B283" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="C283" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D283" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E283" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F283" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G283" s="0">
-        <v>30</v>
-      </c>
-      <c r="H283"/>
-      <c r="I283" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J283" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K283" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L283" s="0">
-        <v>3</v>
-      </c>
-      <c r="M283" s="0">
-        <v>6</v>
-      </c>
-      <c r="N283" s="0">
-        <v>8</v>
-      </c>
-      <c r="O283" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="P283" s="0">
-        <v>8</v>
-      </c>
-      <c r="Q283" s="0">
-        <v>240</v>
-      </c>
-      <c r="R283" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S283" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="0">
-        <v>283</v>
-      </c>
-      <c r="B284" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="C284" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D284" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E284" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F284" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="G284" s="0">
-        <v>30</v>
-      </c>
-      <c r="H284"/>
-      <c r="I284" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J284" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K284" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L284" s="0">
-        <v>3</v>
-      </c>
-      <c r="M284" s="0">
-        <v>6</v>
-      </c>
-      <c r="N284" s="0">
-        <v>8</v>
-      </c>
-      <c r="O284" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="P284" s="0">
-        <v>8</v>
-      </c>
-      <c r="Q284" s="0">
-        <v>240</v>
-      </c>
-      <c r="R284" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S284" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="0">
-        <v>284</v>
-      </c>
-      <c r="B285" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="C285" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D285" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E285" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F285" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="G285" s="0">
-        <v>30</v>
-      </c>
-      <c r="H285"/>
-      <c r="I285" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J285" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K285" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L285" s="0">
-        <v>3</v>
-      </c>
-      <c r="M285" s="0">
-        <v>6</v>
-      </c>
-      <c r="N285" s="0">
-        <v>8</v>
-      </c>
-      <c r="O285" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="P285" s="0">
-        <v>7</v>
-      </c>
-      <c r="Q285" s="0">
-        <v>210</v>
-      </c>
-      <c r="R285" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S285" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="0">
-        <v>285</v>
-      </c>
-      <c r="B286" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="C286" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D286" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E286" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F286" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="G286" s="0">
-        <v>30</v>
-      </c>
-      <c r="H286"/>
-      <c r="I286" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J286" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K286" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L286" s="0">
-        <v>3</v>
-      </c>
-      <c r="M286" s="0">
-        <v>6</v>
-      </c>
-      <c r="N286" s="0">
-        <v>8</v>
-      </c>
-      <c r="O286" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="P286" s="0">
-        <v>7</v>
-      </c>
-      <c r="Q286" s="0">
-        <v>210</v>
-      </c>
-      <c r="R286" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S286" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="0">
-        <v>286</v>
-      </c>
-      <c r="B287" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C287" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D287" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E287" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F287" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G287" s="0">
-        <v>30</v>
-      </c>
-      <c r="H287"/>
-      <c r="I287" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J287" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K287" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L287" s="0">
-        <v>3</v>
-      </c>
-      <c r="M287" s="0">
-        <v>4</v>
-      </c>
-      <c r="N287" s="0">
-        <v>6</v>
-      </c>
-      <c r="O287" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="P287" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q287" s="0">
-        <v>120</v>
-      </c>
-      <c r="R287" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S287" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="0">
-        <v>287</v>
-      </c>
-      <c r="B288" s="0" t="s">
-        <v>198</v>
-      </c>
-      <c r="C288" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D288" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E288" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F288" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G288" s="0">
-        <v>30</v>
-      </c>
-      <c r="H288"/>
-      <c r="I288" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J288" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K288" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L288" s="0">
-        <v>3</v>
-      </c>
-      <c r="M288" s="0">
-        <v>2</v>
-      </c>
-      <c r="N288" s="0">
-        <v>4</v>
-      </c>
-      <c r="O288" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="P288" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q288" s="0">
-        <v>120</v>
-      </c>
-      <c r="R288" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S288" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="0">
-        <v>288</v>
-      </c>
-      <c r="B289" s="0" t="s">
-        <v>199</v>
-      </c>
-      <c r="C289" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D289" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E289" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F289" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="G289" s="0">
-        <v>30</v>
-      </c>
-      <c r="H289"/>
-      <c r="I289" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J289" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K289" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L289" s="0">
-        <v>3</v>
-      </c>
-      <c r="M289" s="0">
-        <v>5</v>
-      </c>
-      <c r="N289" s="0">
-        <v>7</v>
-      </c>
-      <c r="O289" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="P289" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q289" s="0">
-        <v>120</v>
-      </c>
-      <c r="R289" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S289" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="0">
-        <v>289</v>
-      </c>
-      <c r="B290" s="0" t="s">
-        <v>200</v>
-      </c>
-      <c r="C290" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D290" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E290" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F290" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="G290" s="0">
-        <v>30</v>
-      </c>
-      <c r="H290"/>
-      <c r="I290" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J290" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K290" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L290" s="0">
-        <v>3</v>
-      </c>
-      <c r="M290" s="0">
-        <v>2</v>
-      </c>
-      <c r="N290" s="0">
-        <v>4</v>
-      </c>
-      <c r="O290" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="P290" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q290" s="0">
-        <v>120</v>
-      </c>
-      <c r="R290" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S290" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="0">
-        <v>290</v>
-      </c>
-      <c r="B291" s="0" t="s">
-        <v>201</v>
-      </c>
-      <c r="C291" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D291" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E291" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F291" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="G291" s="0">
-        <v>30</v>
-      </c>
-      <c r="H291"/>
-      <c r="I291" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J291" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K291" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L291" s="0">
-        <v>3</v>
-      </c>
-      <c r="M291" s="0">
-        <v>2</v>
-      </c>
-      <c r="N291" s="0">
-        <v>4</v>
-      </c>
-      <c r="O291" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="P291" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q291" s="0">
-        <v>120</v>
-      </c>
-      <c r="R291" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S291" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="0">
-        <v>291</v>
-      </c>
-      <c r="B292" s="0" t="s">
-        <v>202</v>
-      </c>
-      <c r="C292" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D292" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E292" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F292" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G292" s="0">
-        <v>30</v>
-      </c>
-      <c r="H292"/>
-      <c r="I292" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J292" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K292" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L292" s="0">
-        <v>3</v>
-      </c>
-      <c r="M292" s="0">
-        <v>5</v>
-      </c>
-      <c r="N292" s="0">
-        <v>7</v>
-      </c>
-      <c r="O292" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="P292" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q292" s="0">
-        <v>120</v>
-      </c>
-      <c r="R292" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S292" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="0">
-        <v>292</v>
-      </c>
-      <c r="B293" s="0" t="s">
-        <v>203</v>
-      </c>
-      <c r="C293" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D293" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E293" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="F293" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G293" s="0">
-        <v>30</v>
-      </c>
-      <c r="H293"/>
-      <c r="I293" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J293" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K293" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L293" s="0">
-        <v>3</v>
-      </c>
-      <c r="M293" s="0">
-        <v>5</v>
-      </c>
-      <c r="N293" s="0">
-        <v>7</v>
-      </c>
-      <c r="O293" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="P293" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q293" s="0">
-        <v>120</v>
-      </c>
-      <c r="R293" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S293" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="0">
-        <v>293</v>
-      </c>
-      <c r="B294" s="0" t="s">
-        <v>111</v>
-      </c>
-      <c r="C294" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D294" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E294" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F294" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G294" s="0">
-        <v>30</v>
-      </c>
-      <c r="H294"/>
-      <c r="I294" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J294" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K294" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L294" s="0">
-        <v>3</v>
-      </c>
-      <c r="M294" s="0">
-        <v>9</v>
-      </c>
-      <c r="N294" s="0">
-        <v>11</v>
-      </c>
-      <c r="O294" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="P294" s="0">
-        <v>7</v>
-      </c>
-      <c r="Q294" s="0">
-        <v>210</v>
-      </c>
-      <c r="R294" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S294" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="0">
-        <v>294</v>
-      </c>
-      <c r="B295" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="C295" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D295" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E295" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F295" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G295" s="0">
-        <v>30</v>
-      </c>
-      <c r="H295"/>
-      <c r="I295" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J295" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K295" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L295" s="0">
-        <v>3</v>
-      </c>
-      <c r="M295" s="0">
-        <v>9</v>
-      </c>
-      <c r="N295" s="0">
-        <v>11</v>
-      </c>
-      <c r="O295" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="P295" s="0">
-        <v>4</v>
-      </c>
-      <c r="Q295" s="0">
-        <v>120</v>
-      </c>
-      <c r="R295" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S295" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="0">
-        <v>295</v>
-      </c>
-      <c r="B296" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="C296" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="D296" s="0">
-        <v>100000</v>
-      </c>
-      <c r="E296" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F296" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="G296" s="0">
-        <v>30</v>
-      </c>
-      <c r="H296"/>
-      <c r="I296" s="0">
-        <v>100000</v>
-      </c>
-      <c r="J296" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="K296" s="0">
-        <v>10000</v>
-      </c>
-      <c r="L296" s="0">
-        <v>3</v>
-      </c>
-      <c r="M296" s="0">
-        <v>9</v>
-      </c>
-      <c r="N296" s="0">
-        <v>11</v>
-      </c>
-      <c r="O296" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="P296" s="0">
-        <v>7</v>
-      </c>
-      <c r="Q296" s="0">
-        <v>210</v>
-      </c>
-      <c r="R296" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S296" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>
